--- a/InputData/elec/BPSpUGBCD/BAU Subsidy per Unit Grid Battery Capacity Deployed.xlsx
+++ b/InputData/elec/BPSpUGBCD/BAU Subsidy per Unit Grid Battery Capacity Deployed.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\황일서\Dropbox\NEXT Group\20. 프로젝트 관리\2025 에너지 수요전망 모형 구축\EPS 모형\eps-southkorea-3.3.1\InputData\elec\BPSpUGBCD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\administer\Dropbox\kjh\2025\02. EPS\EI\251020_메일회신\회신용 파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1562B92-2262-40BB-9C68-3454A7E4CBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B903464-FC64-4AED-8621-1DAE7F7B69A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Inflation Reduction Act" sheetId="7" r:id="rId2"/>
+    <sheet name="IRA_Modifying by Korea data" sheetId="7" r:id="rId2"/>
     <sheet name="BPSpUGBCD" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
   <si>
     <t>Source:</t>
   </si>
@@ -45,24 +45,7 @@
     <t>Dmnl</t>
   </si>
   <si>
-    <t>incentives in the Inflation Reduction Act. Given the volume of</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This file assumes developers will opt for the battery ITC, given the </t>
-  </si>
-  <si>
-    <t>announced battery manufacturing capacity, we assume projects</t>
-  </si>
-  <si>
-    <t>will qualify for the domestic content bonus.</t>
-  </si>
-  <si>
     <t>Methodology:</t>
-  </si>
-  <si>
-    <t>First, we calculate the percentage of new plants that will qualify for a) the prevailing wage and apprenticeship requirements and b) the domestic content requirements. For part a, we only calculate the share of plants that would meet the apprenticeship requirement and assume all these plants would also meet the prevailing wage requirement (varying assumptions on the share of qualifying plants across scenarios based on data for the construction industry from the ACP Labor Supply Report). For part a, we assume this requirement can be met in every year (which would represent union representation grows by roughly 20% by 2025. For part b, we calculate the domestic content share for each power plant type. For onshore and offshore wind, we assume 100% of plants qualify for the bonus credit, based on a Net Zero America analysis, which lists domestic content shares for various wind components at well over the 55% domestic content requirement. For solar, we use the cited domestic content values for cells, modules, and inverters to calculate a weighted domestic content share, given the percentage of solar capital costs by component from the JEDI model. We assume the domestic content share can increase to meet half the difference between current levels and the 55% requirement by 2026.
-Next, we add in the energy community bonus, assuming that 50% of capacity additions qualify. We then calculate what the total credit value would be for each technology in each year for both the ITC and the PTC. Here, we assume credits start in 2023 and run at their full value through 2032. For the PTC values, we also adjust the calculated credit by the present value over 10 years divided by the present value over the plant lifetime, because the PTC is only available for the first 10 years of a plant's lifetime. Finally, we apply a transferability multiplier of 7.5%. This value reduces the credit value available to developers to account for the fact tax credits are transferable. 
-We limit our analysis to onshore and offshore wind, solar PV, solar thermal, geothermal, municipal solid waste, and battery storage. We do not model credits for qualifying hydro or biogas plants. For solar PV, we calculate a LCOE for both the ITC and PTC settings to determine whether that resource elects the ITC or the PTC in each year.</t>
   </si>
   <si>
     <t>Calculations:</t>
@@ -239,9 +222,6 @@
     <t>Offshore Credit Value % project costs</t>
   </si>
   <si>
-    <t>See Inflation Reduction Act tab</t>
-  </si>
-  <si>
     <t>BPSpUGBCD BAU Percent Subsidy per Unit Grid Battery Capacity Deployed</t>
   </si>
   <si>
@@ -250,9 +230,110 @@
   </si>
   <si>
     <t>https://www.knrec.or.kr/biz/introduce/new_engy/intro_essems.do?gubun=A</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t>한국에너지공단 에너지저장장치 보조금을 출처로 사용하였으며, 계통안정화에 해당하는 저장장치의 보조금 비율을 사용</t>
+    <r>
+      <t xml:space="preserve">The subsidy data were sourced from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Korea Energy Agency (KEA)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>subsidy rate for energy storage systems (ESS) related to grid stabilization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> was applied.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The calculation method used in the U.S. model based on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Inflation Reduction Act (IRA)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> data was adopted, and the model was </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>updated for Korea by modifying the relevant data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>First, we calculate the percentage of new plants that will qualify for a) the prevailing wage and apprenticeship requirements and b) the domestic content requirements. For part a, we only calculate the share of plants that would meet the apprenticeship requirement and assume all these plants would also meet the prevailing wage requirement (varying assumptions on the share of qualifying plants across scenarios based on data for the construction industry from the ACP Labor Supply Report). For part a, we assume this requirement can be met in every year (which would represent union representation grows by roughly 20% by 2025. For part b, we calculate the domestic content share for each power plant type. For onshore and offshore wind, we assume 100% of plants qualify for the bonus credit, based on a Net Zero America analysis, which lists domestic content shares for various wind components at well over the 55% domestic content requirement. For solar, we use the cited domestic content values for cells, modules, and inverters to calculate a weighted domestic content share, given the percentage of solar capital costs by component from the JEDI model. We assume the domestic content share can increase to meet half the difference between current levels and the 55% requirement by 2026.
+Next, we add in the energy community bonus, assuming that 50% of capacity additions qualify. We then calculate what the total credit value would be for each technology in each year for both the ITC and the PTC. Here, we assume credits start in 2023 and run at their full value through 2032. For the PTC values, we also adjust the calculated credit by the present value over 10 years divided by the present value over the plant lifetime, because the PTC is only available for the first 10 years of a plant's lifetime. Finally, we apply a transferability multiplier of 7.5%. This value reduces the credit value available to developers to account for the fact tax credits are transferable. 
+We limit our analysis to onshore and offshore wind, solar PV, solar thermal, geothermal, municipal solid waste, and battery storage. We do not model credits for qualifying hydro or biogas plants. For solar PV, we calculate a LCOE for both the ITC and PTC settings to determine whether that resource elects the ITC or the PTC in each year.</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
@@ -265,7 +346,7 @@
     <numFmt numFmtId="177" formatCode="0.000"/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -394,6 +475,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -502,15 +600,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -590,14 +689,16 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="177" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Currency 2" xfId="5" xr:uid="{81BD210F-5FF0-4880-8028-0DC76957F95F}"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{A0D66D47-893E-4339-ABA2-2AA2E8FD27AB}"/>
     <cellStyle name="Normal 3 2" xfId="3" xr:uid="{6280AA9E-3B50-418D-82DE-98EB684B0878}"/>
     <cellStyle name="Percent 2" xfId="4" xr:uid="{2FFD538B-3558-46F7-AC70-5718F1F53027}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="6" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -942,61 +1043,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B3" s="43" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{ECD69332-3E5D-4725-8E24-764E54917661}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1006,22 +1090,22 @@
     <tabColor rgb="FF6AA84F"/>
   </sheetPr>
   <dimension ref="A1:AJ534"/>
-  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="94.3984375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="15.3984375" style="5" customWidth="1"/>
-    <col min="3" max="4" width="11.59765625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="10.09765625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="7.59765625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="9.59765625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="10.09765625" style="5" customWidth="1"/>
-    <col min="9" max="36" width="7.59765625" style="5" customWidth="1"/>
-    <col min="37" max="16384" width="12.59765625" style="5"/>
+    <col min="1" max="1" width="94.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="15.375" style="5" customWidth="1"/>
+    <col min="3" max="4" width="11.625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="10.125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="7.625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="9.625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10.125" style="5" customWidth="1"/>
+    <col min="9" max="36" width="7.625" style="5" customWidth="1"/>
+    <col min="37" max="16384" width="12.625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1059,9 +1143,9 @@
       <c r="AI1" s="4"/>
       <c r="AJ1" s="4"/>
     </row>
-    <row r="2" spans="1:36" ht="305.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" ht="305.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1099,7 +1183,7 @@
       <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
     </row>
-    <row r="3" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1137,9 +1221,9 @@
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
     </row>
-    <row r="4" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1177,9 +1261,9 @@
       <c r="AI4" s="7"/>
       <c r="AJ4" s="7"/>
     </row>
-    <row r="5" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1217,9 +1301,9 @@
       <c r="AI5" s="9"/>
       <c r="AJ5" s="9"/>
     </row>
-    <row r="6" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1257,9 +1341,9 @@
       <c r="AI6" s="4"/>
       <c r="AJ6" s="4"/>
     </row>
-    <row r="7" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1297,7 +1381,7 @@
       <c r="AI7" s="4"/>
       <c r="AJ7" s="4"/>
     </row>
-    <row r="8" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1335,7 +1419,7 @@
       <c r="AI8" s="4"/>
       <c r="AJ8" s="4"/>
     </row>
-    <row r="9" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1373,7 +1457,7 @@
       <c r="AI9" s="4"/>
       <c r="AJ9" s="4"/>
     </row>
-    <row r="10" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -1411,7 +1495,7 @@
       <c r="AI10" s="4"/>
       <c r="AJ10" s="4"/>
     </row>
-    <row r="11" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1449,7 +1533,7 @@
       <c r="AI11" s="4"/>
       <c r="AJ11" s="4"/>
     </row>
-    <row r="12" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1487,7 +1571,7 @@
       <c r="AI12" s="4"/>
       <c r="AJ12" s="4"/>
     </row>
-    <row r="13" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1525,7 +1609,7 @@
       <c r="AI13" s="4"/>
       <c r="AJ13" s="4"/>
     </row>
-    <row r="14" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -1563,7 +1647,7 @@
       <c r="AI14" s="4"/>
       <c r="AJ14" s="4"/>
     </row>
-    <row r="15" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1601,7 +1685,7 @@
       <c r="AI15" s="4"/>
       <c r="AJ15" s="4"/>
     </row>
-    <row r="16" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1639,7 +1723,7 @@
       <c r="AI16" s="4"/>
       <c r="AJ16" s="4"/>
     </row>
-    <row r="17" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -1677,7 +1761,7 @@
       <c r="AI17" s="4"/>
       <c r="AJ17" s="4"/>
     </row>
-    <row r="18" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A18" s="12"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1715,7 +1799,7 @@
       <c r="AI18" s="4"/>
       <c r="AJ18" s="4"/>
     </row>
-    <row r="19" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1753,7 +1837,7 @@
       <c r="AI19" s="4"/>
       <c r="AJ19" s="4"/>
     </row>
-    <row r="20" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1791,7 +1875,7 @@
       <c r="AI20" s="4"/>
       <c r="AJ20" s="4"/>
     </row>
-    <row r="21" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1829,7 +1913,7 @@
       <c r="AI21" s="4"/>
       <c r="AJ21" s="4"/>
     </row>
-    <row r="22" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A22" s="12"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1867,7 +1951,7 @@
       <c r="AI22" s="4"/>
       <c r="AJ22" s="4"/>
     </row>
-    <row r="23" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1905,7 +1989,7 @@
       <c r="AI23" s="4"/>
       <c r="AJ23" s="4"/>
     </row>
-    <row r="24" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1943,7 +2027,7 @@
       <c r="AI24" s="4"/>
       <c r="AJ24" s="4"/>
     </row>
-    <row r="25" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1981,9 +2065,9 @@
       <c r="AI25" s="4"/>
       <c r="AJ25" s="4"/>
     </row>
-    <row r="26" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -2021,9 +2105,9 @@
       <c r="AI26" s="4"/>
       <c r="AJ26" s="4"/>
     </row>
-    <row r="27" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -2061,9 +2145,9 @@
       <c r="AI27" s="4"/>
       <c r="AJ27" s="4"/>
     </row>
-    <row r="28" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -2101,9 +2185,9 @@
       <c r="AI28" s="4"/>
       <c r="AJ28" s="4"/>
     </row>
-    <row r="29" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B29" s="13">
         <v>0.127</v>
@@ -2143,9 +2227,9 @@
       <c r="AI29" s="4"/>
       <c r="AJ29" s="4"/>
     </row>
-    <row r="30" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B30" s="14">
         <f>B29*1.2</f>
@@ -2186,7 +2270,7 @@
       <c r="AI30" s="4"/>
       <c r="AJ30" s="4"/>
     </row>
-    <row r="31" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -2224,7 +2308,7 @@
       <c r="AI31" s="4"/>
       <c r="AJ31" s="4"/>
     </row>
-    <row r="32" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="12">
         <v>2022</v>
@@ -2320,9 +2404,9 @@
       <c r="AI32" s="4"/>
       <c r="AJ32" s="4"/>
     </row>
-    <row r="33" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B33" s="13">
         <v>0</v>
@@ -2418,9 +2502,9 @@
       <c r="AI33" s="4"/>
       <c r="AJ33" s="4"/>
     </row>
-    <row r="34" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B34" s="13">
         <f>B33</f>
@@ -2517,7 +2601,7 @@
       <c r="AI34" s="4"/>
       <c r="AJ34" s="4"/>
     </row>
-    <row r="35" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -2555,9 +2639,9 @@
       <c r="AI35" s="4"/>
       <c r="AJ35" s="4"/>
     </row>
-    <row r="36" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -2595,9 +2679,9 @@
       <c r="AI36" s="9"/>
       <c r="AJ36" s="9"/>
     </row>
-    <row r="37" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -2635,9 +2719,9 @@
       <c r="AI37" s="4"/>
       <c r="AJ37" s="4"/>
     </row>
-    <row r="38" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -2675,7 +2759,7 @@
       <c r="AI38" s="4"/>
       <c r="AJ38" s="4"/>
     </row>
-    <row r="39" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -2713,16 +2797,16 @@
       <c r="AI39" s="4"/>
       <c r="AJ39" s="4"/>
     </row>
-    <row r="40" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="17" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -2757,12 +2841,12 @@
       <c r="AI40" s="4"/>
       <c r="AJ40" s="4"/>
     </row>
-    <row r="41" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -2799,9 +2883,9 @@
       <c r="AI41" s="4"/>
       <c r="AJ41" s="4"/>
     </row>
-    <row r="42" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B42" s="22">
         <v>0.41199999999999998</v>
@@ -2843,9 +2927,9 @@
       <c r="AI42" s="4"/>
       <c r="AJ42" s="4"/>
     </row>
-    <row r="43" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B43" s="22">
         <v>0.13200000000000001</v>
@@ -2887,9 +2971,9 @@
       <c r="AI43" s="4"/>
       <c r="AJ43" s="4"/>
     </row>
-    <row r="44" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B44" s="22">
         <v>0.114</v>
@@ -2931,9 +3015,9 @@
       <c r="AI44" s="4"/>
       <c r="AJ44" s="4"/>
     </row>
-    <row r="45" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B45" s="22">
         <v>7.0000000000000007E-2</v>
@@ -2973,9 +3057,9 @@
       <c r="AI45" s="4"/>
       <c r="AJ45" s="4"/>
     </row>
-    <row r="46" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B46" s="22">
         <v>8.7999999999999995E-2</v>
@@ -3015,9 +3099,9 @@
       <c r="AI46" s="4"/>
       <c r="AJ46" s="4"/>
     </row>
-    <row r="47" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B47" s="22">
         <v>5.2999999999999999E-2</v>
@@ -3057,9 +3141,9 @@
       <c r="AI47" s="4"/>
       <c r="AJ47" s="4"/>
     </row>
-    <row r="48" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B48" s="22">
         <v>4.3999999999999997E-2</v>
@@ -3099,9 +3183,9 @@
       <c r="AI48" s="4"/>
       <c r="AJ48" s="4"/>
     </row>
-    <row r="49" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A49" s="21" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B49" s="22">
         <v>1.7999999999999999E-2</v>
@@ -3141,9 +3225,9 @@
       <c r="AI49" s="4"/>
       <c r="AJ49" s="4"/>
     </row>
-    <row r="50" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B50" s="22">
         <v>2.5999999999999999E-2</v>
@@ -3183,9 +3267,9 @@
       <c r="AI50" s="4"/>
       <c r="AJ50" s="4"/>
     </row>
-    <row r="51" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A51" s="24" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B51" s="25">
         <v>4.3999999999999997E-2</v>
@@ -3225,7 +3309,7 @@
       <c r="AI51" s="4"/>
       <c r="AJ51" s="4"/>
     </row>
-    <row r="52" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A52" s="12"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -3263,9 +3347,9 @@
       <c r="AI52" s="4"/>
       <c r="AJ52" s="4"/>
     </row>
-    <row r="53" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B53" s="23">
         <f>SUMPRODUCT(B42:B44,D42:D44)/SUM(B42:B44)</f>
@@ -3306,9 +3390,9 @@
       <c r="AI53" s="4"/>
       <c r="AJ53" s="4"/>
     </row>
-    <row r="54" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B54" s="23">
         <f>AVERAGE(H62,B53)</f>
@@ -3349,7 +3433,7 @@
       <c r="AI54" s="4"/>
       <c r="AJ54" s="4"/>
     </row>
-    <row r="55" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="23"/>
       <c r="C55" s="4"/>
@@ -3387,7 +3471,7 @@
       <c r="AI55" s="4"/>
       <c r="AJ55" s="4"/>
     </row>
-    <row r="56" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="12">
         <v>2022</v>
@@ -3439,9 +3523,9 @@
       <c r="AI56" s="4"/>
       <c r="AJ56" s="4"/>
     </row>
-    <row r="57" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B57" s="23">
         <f>B53</f>
@@ -3499,7 +3583,7 @@
       <c r="AI57" s="4"/>
       <c r="AJ57" s="4"/>
     </row>
-    <row r="58" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -3537,9 +3621,9 @@
       <c r="AI58" s="4"/>
       <c r="AJ58" s="4"/>
     </row>
-    <row r="59" spans="1:36" ht="31.2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:36" ht="27" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -3577,7 +3661,7 @@
       <c r="AI59" s="4"/>
       <c r="AJ59" s="4"/>
     </row>
-    <row r="60" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -3615,7 +3699,7 @@
       <c r="AI60" s="12"/>
       <c r="AJ60" s="12"/>
     </row>
-    <row r="61" spans="1:36" s="26" customFormat="1" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:36" s="26" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A61" s="15"/>
       <c r="B61" s="15">
         <v>2022</v>
@@ -3711,9 +3795,9 @@
       <c r="AI61" s="12"/>
       <c r="AJ61" s="12"/>
     </row>
-    <row r="62" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A62" s="23" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B62" s="27">
         <v>0.4</v>
@@ -3809,9 +3893,9 @@
       <c r="AI62" s="23"/>
       <c r="AJ62" s="23"/>
     </row>
-    <row r="63" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A63" s="23" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B63" s="27">
         <f>B53</f>
@@ -3936,9 +4020,9 @@
       <c r="AI63" s="23"/>
       <c r="AJ63" s="23"/>
     </row>
-    <row r="64" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B64" s="27">
         <f>B63/B62</f>
@@ -4063,7 +4147,7 @@
       <c r="AI64" s="4"/>
       <c r="AJ64" s="4"/>
     </row>
-    <row r="65" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A65" s="10"/>
       <c r="B65" s="27"/>
       <c r="C65" s="27"/>
@@ -4101,9 +4185,9 @@
       <c r="AI65" s="12"/>
       <c r="AJ65" s="12"/>
     </row>
-    <row r="66" spans="1:36" s="29" customFormat="1" ht="31.2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:36" s="29" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B66" s="28">
         <v>1</v>
@@ -4199,7 +4283,7 @@
       <c r="AI66" s="15"/>
       <c r="AJ66" s="15"/>
     </row>
-    <row r="67" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A67" s="12"/>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
@@ -4237,7 +4321,7 @@
       <c r="AI67" s="12"/>
       <c r="AJ67" s="12"/>
     </row>
-    <row r="68" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>1</v>
       </c>
@@ -4277,9 +4361,9 @@
       <c r="AI68" s="9"/>
       <c r="AJ68" s="9"/>
     </row>
-    <row r="69" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -4317,9 +4401,9 @@
       <c r="AI69" s="4"/>
       <c r="AJ69" s="4"/>
     </row>
-    <row r="70" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -4357,9 +4441,9 @@
       <c r="AI70" s="4"/>
       <c r="AJ70" s="4"/>
     </row>
-    <row r="71" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -4397,7 +4481,7 @@
       <c r="AI71" s="4"/>
       <c r="AJ71" s="4"/>
     </row>
-    <row r="72" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -4435,9 +4519,9 @@
       <c r="AI72" s="4"/>
       <c r="AJ72" s="4"/>
     </row>
-    <row r="73" spans="1:36" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:36" s="35" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A73" s="32" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B73" s="38"/>
       <c r="C73" s="38"/>
@@ -4475,9 +4559,9 @@
       <c r="AI73" s="34"/>
       <c r="AJ73" s="34"/>
     </row>
-    <row r="74" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A74" s="30" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B74" s="30">
         <v>2022</v>
@@ -4573,9 +4657,9 @@
       <c r="AI74" s="4"/>
       <c r="AJ74" s="4"/>
     </row>
-    <row r="75" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A75" s="30" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B75" s="36">
         <v>0</v>
@@ -4671,7 +4755,7 @@
       <c r="AI75" s="4"/>
       <c r="AJ75" s="4"/>
     </row>
-    <row r="76" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A76" s="12"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -4709,9 +4793,9 @@
       <c r="AI76" s="4"/>
       <c r="AJ76" s="4"/>
     </row>
-    <row r="77" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A77" s="30" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B77" s="39">
         <v>0.06</v>
@@ -4751,9 +4835,9 @@
       <c r="AI77" s="4"/>
       <c r="AJ77" s="4"/>
     </row>
-    <row r="78" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A78" s="30" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B78" s="39">
         <v>0.3</v>
@@ -4793,9 +4877,9 @@
       <c r="AI78" s="4"/>
       <c r="AJ78" s="4"/>
     </row>
-    <row r="79" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A79" s="30" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B79" s="39">
         <v>0.02</v>
@@ -4835,9 +4919,9 @@
       <c r="AI79" s="4"/>
       <c r="AJ79" s="4"/>
     </row>
-    <row r="80" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A80" s="30" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B80" s="39">
         <v>0.1</v>
@@ -4877,9 +4961,9 @@
       <c r="AI80" s="4"/>
       <c r="AJ80" s="4"/>
     </row>
-    <row r="81" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B81" s="23">
         <v>7.4999999999999997E-2</v>
@@ -4919,9 +5003,9 @@
       <c r="AI81" s="4"/>
       <c r="AJ81" s="4"/>
     </row>
-    <row r="82" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A82" s="30" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B82" s="31">
         <v>0.1</v>
@@ -4961,9 +5045,9 @@
       <c r="AI82" s="4"/>
       <c r="AJ82" s="4"/>
     </row>
-    <row r="83" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A83" s="30" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B83" s="31">
         <v>0.5</v>
@@ -5003,7 +5087,7 @@
       <c r="AI83" s="4"/>
       <c r="AJ83" s="4"/>
     </row>
-    <row r="84" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -5041,9 +5125,9 @@
       <c r="AI84" s="4"/>
       <c r="AJ84" s="4"/>
     </row>
-    <row r="85" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A85" s="40" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -5081,7 +5165,7 @@
       <c r="AI85" s="4"/>
       <c r="AJ85" s="4"/>
     </row>
-    <row r="86" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A86" s="30"/>
       <c r="B86" s="30"/>
       <c r="C86" s="30"/>
@@ -5119,7 +5203,7 @@
       <c r="AI86" s="4"/>
       <c r="AJ86" s="4"/>
     </row>
-    <row r="87" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A87" s="30"/>
       <c r="B87" s="30">
         <v>2023</v>
@@ -5213,9 +5297,9 @@
       <c r="AI87" s="4"/>
       <c r="AJ87" s="4"/>
     </row>
-    <row r="88" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B88" s="37">
         <f t="shared" ref="B88:C88" si="4">C88</f>
@@ -5337,7 +5421,7 @@
       <c r="AI88" s="4"/>
       <c r="AJ88" s="4"/>
     </row>
-    <row r="89" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
@@ -5375,7 +5459,7 @@
       <c r="AI89" s="12"/>
       <c r="AJ89" s="12"/>
     </row>
-    <row r="90" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -5413,7 +5497,7 @@
       <c r="AI90" s="4"/>
       <c r="AJ90" s="4"/>
     </row>
-    <row r="91" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -5451,7 +5535,7 @@
       <c r="AI91" s="4"/>
       <c r="AJ91" s="4"/>
     </row>
-    <row r="92" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -5489,7 +5573,7 @@
       <c r="AI92" s="4"/>
       <c r="AJ92" s="4"/>
     </row>
-    <row r="93" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -5527,7 +5611,7 @@
       <c r="AI93" s="4"/>
       <c r="AJ93" s="4"/>
     </row>
-    <row r="94" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -5565,7 +5649,7 @@
       <c r="AI94" s="4"/>
       <c r="AJ94" s="4"/>
     </row>
-    <row r="95" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -5603,7 +5687,7 @@
       <c r="AI95" s="4"/>
       <c r="AJ95" s="4"/>
     </row>
-    <row r="96" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -5641,7 +5725,7 @@
       <c r="AI96" s="4"/>
       <c r="AJ96" s="4"/>
     </row>
-    <row r="97" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -5679,7 +5763,7 @@
       <c r="AI97" s="4"/>
       <c r="AJ97" s="4"/>
     </row>
-    <row r="98" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -5717,7 +5801,7 @@
       <c r="AI98" s="4"/>
       <c r="AJ98" s="4"/>
     </row>
-    <row r="99" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -5755,7 +5839,7 @@
       <c r="AI99" s="4"/>
       <c r="AJ99" s="4"/>
     </row>
-    <row r="100" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -5793,7 +5877,7 @@
       <c r="AI100" s="4"/>
       <c r="AJ100" s="4"/>
     </row>
-    <row r="101" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -5831,7 +5915,7 @@
       <c r="AI101" s="4"/>
       <c r="AJ101" s="4"/>
     </row>
-    <row r="102" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -5869,7 +5953,7 @@
       <c r="AI102" s="4"/>
       <c r="AJ102" s="4"/>
     </row>
-    <row r="103" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -5907,7 +5991,7 @@
       <c r="AI103" s="4"/>
       <c r="AJ103" s="4"/>
     </row>
-    <row r="104" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -5945,7 +6029,7 @@
       <c r="AI104" s="4"/>
       <c r="AJ104" s="4"/>
     </row>
-    <row r="105" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -5983,7 +6067,7 @@
       <c r="AI105" s="4"/>
       <c r="AJ105" s="4"/>
     </row>
-    <row r="106" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -6021,7 +6105,7 @@
       <c r="AI106" s="4"/>
       <c r="AJ106" s="4"/>
     </row>
-    <row r="107" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -6059,7 +6143,7 @@
       <c r="AI107" s="4"/>
       <c r="AJ107" s="4"/>
     </row>
-    <row r="108" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -6097,7 +6181,7 @@
       <c r="AI108" s="4"/>
       <c r="AJ108" s="4"/>
     </row>
-    <row r="109" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -6135,7 +6219,7 @@
       <c r="AI109" s="4"/>
       <c r="AJ109" s="4"/>
     </row>
-    <row r="110" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -6173,7 +6257,7 @@
       <c r="AI110" s="4"/>
       <c r="AJ110" s="4"/>
     </row>
-    <row r="111" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -6211,7 +6295,7 @@
       <c r="AI111" s="4"/>
       <c r="AJ111" s="4"/>
     </row>
-    <row r="112" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -6249,7 +6333,7 @@
       <c r="AI112" s="4"/>
       <c r="AJ112" s="4"/>
     </row>
-    <row r="113" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -6287,7 +6371,7 @@
       <c r="AI113" s="4"/>
       <c r="AJ113" s="4"/>
     </row>
-    <row r="114" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -6325,7 +6409,7 @@
       <c r="AI114" s="4"/>
       <c r="AJ114" s="4"/>
     </row>
-    <row r="115" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -6363,7 +6447,7 @@
       <c r="AI115" s="4"/>
       <c r="AJ115" s="4"/>
     </row>
-    <row r="116" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -6401,7 +6485,7 @@
       <c r="AI116" s="4"/>
       <c r="AJ116" s="4"/>
     </row>
-    <row r="117" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -6439,7 +6523,7 @@
       <c r="AI117" s="4"/>
       <c r="AJ117" s="4"/>
     </row>
-    <row r="118" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -6477,7 +6561,7 @@
       <c r="AI118" s="4"/>
       <c r="AJ118" s="4"/>
     </row>
-    <row r="119" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -6515,7 +6599,7 @@
       <c r="AI119" s="4"/>
       <c r="AJ119" s="4"/>
     </row>
-    <row r="120" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -6553,7 +6637,7 @@
       <c r="AI120" s="4"/>
       <c r="AJ120" s="4"/>
     </row>
-    <row r="121" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -6591,7 +6675,7 @@
       <c r="AI121" s="4"/>
       <c r="AJ121" s="4"/>
     </row>
-    <row r="122" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -6629,7 +6713,7 @@
       <c r="AI122" s="4"/>
       <c r="AJ122" s="4"/>
     </row>
-    <row r="123" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -6667,7 +6751,7 @@
       <c r="AI123" s="4"/>
       <c r="AJ123" s="4"/>
     </row>
-    <row r="124" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -6705,7 +6789,7 @@
       <c r="AI124" s="4"/>
       <c r="AJ124" s="4"/>
     </row>
-    <row r="125" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -6743,7 +6827,7 @@
       <c r="AI125" s="4"/>
       <c r="AJ125" s="4"/>
     </row>
-    <row r="126" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -6781,7 +6865,7 @@
       <c r="AI126" s="4"/>
       <c r="AJ126" s="4"/>
     </row>
-    <row r="127" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -6819,7 +6903,7 @@
       <c r="AI127" s="4"/>
       <c r="AJ127" s="4"/>
     </row>
-    <row r="128" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -6857,7 +6941,7 @@
       <c r="AI128" s="4"/>
       <c r="AJ128" s="4"/>
     </row>
-    <row r="129" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -6895,7 +6979,7 @@
       <c r="AI129" s="4"/>
       <c r="AJ129" s="4"/>
     </row>
-    <row r="130" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -6933,7 +7017,7 @@
       <c r="AI130" s="4"/>
       <c r="AJ130" s="4"/>
     </row>
-    <row r="131" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -6971,7 +7055,7 @@
       <c r="AI131" s="4"/>
       <c r="AJ131" s="4"/>
     </row>
-    <row r="132" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -7009,7 +7093,7 @@
       <c r="AI132" s="4"/>
       <c r="AJ132" s="4"/>
     </row>
-    <row r="133" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -7047,7 +7131,7 @@
       <c r="AI133" s="4"/>
       <c r="AJ133" s="4"/>
     </row>
-    <row r="134" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -7085,7 +7169,7 @@
       <c r="AI134" s="4"/>
       <c r="AJ134" s="4"/>
     </row>
-    <row r="135" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -7123,7 +7207,7 @@
       <c r="AI135" s="4"/>
       <c r="AJ135" s="4"/>
     </row>
-    <row r="136" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -7161,7 +7245,7 @@
       <c r="AI136" s="4"/>
       <c r="AJ136" s="4"/>
     </row>
-    <row r="137" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -7199,7 +7283,7 @@
       <c r="AI137" s="4"/>
       <c r="AJ137" s="4"/>
     </row>
-    <row r="138" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -7237,7 +7321,7 @@
       <c r="AI138" s="4"/>
       <c r="AJ138" s="4"/>
     </row>
-    <row r="139" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -7275,7 +7359,7 @@
       <c r="AI139" s="4"/>
       <c r="AJ139" s="4"/>
     </row>
-    <row r="140" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -7313,7 +7397,7 @@
       <c r="AI140" s="4"/>
       <c r="AJ140" s="4"/>
     </row>
-    <row r="141" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -7351,7 +7435,7 @@
       <c r="AI141" s="4"/>
       <c r="AJ141" s="4"/>
     </row>
-    <row r="142" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -7389,7 +7473,7 @@
       <c r="AI142" s="4"/>
       <c r="AJ142" s="4"/>
     </row>
-    <row r="143" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -7427,7 +7511,7 @@
       <c r="AI143" s="4"/>
       <c r="AJ143" s="4"/>
     </row>
-    <row r="144" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -7465,7 +7549,7 @@
       <c r="AI144" s="4"/>
       <c r="AJ144" s="4"/>
     </row>
-    <row r="145" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -7503,7 +7587,7 @@
       <c r="AI145" s="4"/>
       <c r="AJ145" s="4"/>
     </row>
-    <row r="146" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -7541,7 +7625,7 @@
       <c r="AI146" s="4"/>
       <c r="AJ146" s="4"/>
     </row>
-    <row r="147" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -7579,7 +7663,7 @@
       <c r="AI147" s="4"/>
       <c r="AJ147" s="4"/>
     </row>
-    <row r="148" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -7617,7 +7701,7 @@
       <c r="AI148" s="4"/>
       <c r="AJ148" s="4"/>
     </row>
-    <row r="149" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -7655,7 +7739,7 @@
       <c r="AI149" s="4"/>
       <c r="AJ149" s="4"/>
     </row>
-    <row r="150" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -7693,7 +7777,7 @@
       <c r="AI150" s="4"/>
       <c r="AJ150" s="4"/>
     </row>
-    <row r="151" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -7731,7 +7815,7 @@
       <c r="AI151" s="4"/>
       <c r="AJ151" s="4"/>
     </row>
-    <row r="152" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -7769,7 +7853,7 @@
       <c r="AI152" s="4"/>
       <c r="AJ152" s="4"/>
     </row>
-    <row r="153" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -7807,7 +7891,7 @@
       <c r="AI153" s="4"/>
       <c r="AJ153" s="4"/>
     </row>
-    <row r="154" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -7845,7 +7929,7 @@
       <c r="AI154" s="4"/>
       <c r="AJ154" s="4"/>
     </row>
-    <row r="155" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -7883,7 +7967,7 @@
       <c r="AI155" s="4"/>
       <c r="AJ155" s="4"/>
     </row>
-    <row r="156" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -7921,7 +8005,7 @@
       <c r="AI156" s="4"/>
       <c r="AJ156" s="4"/>
     </row>
-    <row r="157" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -7959,7 +8043,7 @@
       <c r="AI157" s="4"/>
       <c r="AJ157" s="4"/>
     </row>
-    <row r="158" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -7997,7 +8081,7 @@
       <c r="AI158" s="4"/>
       <c r="AJ158" s="4"/>
     </row>
-    <row r="159" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -8035,7 +8119,7 @@
       <c r="AI159" s="4"/>
       <c r="AJ159" s="4"/>
     </row>
-    <row r="160" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -8073,7 +8157,7 @@
       <c r="AI160" s="4"/>
       <c r="AJ160" s="4"/>
     </row>
-    <row r="161" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -8111,7 +8195,7 @@
       <c r="AI161" s="4"/>
       <c r="AJ161" s="4"/>
     </row>
-    <row r="162" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -8149,7 +8233,7 @@
       <c r="AI162" s="4"/>
       <c r="AJ162" s="4"/>
     </row>
-    <row r="163" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -8187,7 +8271,7 @@
       <c r="AI163" s="4"/>
       <c r="AJ163" s="4"/>
     </row>
-    <row r="164" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -8225,7 +8309,7 @@
       <c r="AI164" s="4"/>
       <c r="AJ164" s="4"/>
     </row>
-    <row r="165" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -8263,7 +8347,7 @@
       <c r="AI165" s="4"/>
       <c r="AJ165" s="4"/>
     </row>
-    <row r="166" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -8301,7 +8385,7 @@
       <c r="AI166" s="4"/>
       <c r="AJ166" s="4"/>
     </row>
-    <row r="167" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -8339,7 +8423,7 @@
       <c r="AI167" s="4"/>
       <c r="AJ167" s="4"/>
     </row>
-    <row r="168" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -8377,7 +8461,7 @@
       <c r="AI168" s="4"/>
       <c r="AJ168" s="4"/>
     </row>
-    <row r="169" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -8415,7 +8499,7 @@
       <c r="AI169" s="4"/>
       <c r="AJ169" s="4"/>
     </row>
-    <row r="170" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -8453,7 +8537,7 @@
       <c r="AI170" s="4"/>
       <c r="AJ170" s="4"/>
     </row>
-    <row r="171" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -8491,7 +8575,7 @@
       <c r="AI171" s="4"/>
       <c r="AJ171" s="4"/>
     </row>
-    <row r="172" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -8529,7 +8613,7 @@
       <c r="AI172" s="4"/>
       <c r="AJ172" s="4"/>
     </row>
-    <row r="173" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -8567,7 +8651,7 @@
       <c r="AI173" s="4"/>
       <c r="AJ173" s="4"/>
     </row>
-    <row r="174" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -8605,7 +8689,7 @@
       <c r="AI174" s="4"/>
       <c r="AJ174" s="4"/>
     </row>
-    <row r="175" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -8643,7 +8727,7 @@
       <c r="AI175" s="4"/>
       <c r="AJ175" s="4"/>
     </row>
-    <row r="176" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -8681,7 +8765,7 @@
       <c r="AI176" s="4"/>
       <c r="AJ176" s="4"/>
     </row>
-    <row r="177" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -8719,7 +8803,7 @@
       <c r="AI177" s="4"/>
       <c r="AJ177" s="4"/>
     </row>
-    <row r="178" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -8757,7 +8841,7 @@
       <c r="AI178" s="4"/>
       <c r="AJ178" s="4"/>
     </row>
-    <row r="179" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -8795,7 +8879,7 @@
       <c r="AI179" s="4"/>
       <c r="AJ179" s="4"/>
     </row>
-    <row r="180" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -8833,7 +8917,7 @@
       <c r="AI180" s="4"/>
       <c r="AJ180" s="4"/>
     </row>
-    <row r="181" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -8871,7 +8955,7 @@
       <c r="AI181" s="4"/>
       <c r="AJ181" s="4"/>
     </row>
-    <row r="182" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -8909,7 +8993,7 @@
       <c r="AI182" s="4"/>
       <c r="AJ182" s="4"/>
     </row>
-    <row r="183" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -8947,7 +9031,7 @@
       <c r="AI183" s="4"/>
       <c r="AJ183" s="4"/>
     </row>
-    <row r="184" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -8985,7 +9069,7 @@
       <c r="AI184" s="4"/>
       <c r="AJ184" s="4"/>
     </row>
-    <row r="185" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -9023,7 +9107,7 @@
       <c r="AI185" s="4"/>
       <c r="AJ185" s="4"/>
     </row>
-    <row r="186" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -9061,7 +9145,7 @@
       <c r="AI186" s="4"/>
       <c r="AJ186" s="4"/>
     </row>
-    <row r="187" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -9099,7 +9183,7 @@
       <c r="AI187" s="4"/>
       <c r="AJ187" s="4"/>
     </row>
-    <row r="188" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -9137,7 +9221,7 @@
       <c r="AI188" s="4"/>
       <c r="AJ188" s="4"/>
     </row>
-    <row r="189" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -9175,7 +9259,7 @@
       <c r="AI189" s="4"/>
       <c r="AJ189" s="4"/>
     </row>
-    <row r="190" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -9213,7 +9297,7 @@
       <c r="AI190" s="4"/>
       <c r="AJ190" s="4"/>
     </row>
-    <row r="191" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -9251,7 +9335,7 @@
       <c r="AI191" s="4"/>
       <c r="AJ191" s="4"/>
     </row>
-    <row r="192" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -9289,7 +9373,7 @@
       <c r="AI192" s="4"/>
       <c r="AJ192" s="4"/>
     </row>
-    <row r="193" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -9327,7 +9411,7 @@
       <c r="AI193" s="4"/>
       <c r="AJ193" s="4"/>
     </row>
-    <row r="194" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -9365,7 +9449,7 @@
       <c r="AI194" s="4"/>
       <c r="AJ194" s="4"/>
     </row>
-    <row r="195" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -9403,7 +9487,7 @@
       <c r="AI195" s="4"/>
       <c r="AJ195" s="4"/>
     </row>
-    <row r="196" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -9441,7 +9525,7 @@
       <c r="AI196" s="4"/>
       <c r="AJ196" s="4"/>
     </row>
-    <row r="197" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -9479,7 +9563,7 @@
       <c r="AI197" s="4"/>
       <c r="AJ197" s="4"/>
     </row>
-    <row r="198" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -9517,7 +9601,7 @@
       <c r="AI198" s="4"/>
       <c r="AJ198" s="4"/>
     </row>
-    <row r="199" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -9555,7 +9639,7 @@
       <c r="AI199" s="4"/>
       <c r="AJ199" s="4"/>
     </row>
-    <row r="200" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -9593,7 +9677,7 @@
       <c r="AI200" s="4"/>
       <c r="AJ200" s="4"/>
     </row>
-    <row r="201" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -9631,7 +9715,7 @@
       <c r="AI201" s="4"/>
       <c r="AJ201" s="4"/>
     </row>
-    <row r="202" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -9669,7 +9753,7 @@
       <c r="AI202" s="4"/>
       <c r="AJ202" s="4"/>
     </row>
-    <row r="203" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -9707,7 +9791,7 @@
       <c r="AI203" s="4"/>
       <c r="AJ203" s="4"/>
     </row>
-    <row r="204" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -9745,7 +9829,7 @@
       <c r="AI204" s="4"/>
       <c r="AJ204" s="4"/>
     </row>
-    <row r="205" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -9783,7 +9867,7 @@
       <c r="AI205" s="4"/>
       <c r="AJ205" s="4"/>
     </row>
-    <row r="206" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -9821,7 +9905,7 @@
       <c r="AI206" s="4"/>
       <c r="AJ206" s="4"/>
     </row>
-    <row r="207" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -9859,7 +9943,7 @@
       <c r="AI207" s="4"/>
       <c r="AJ207" s="4"/>
     </row>
-    <row r="208" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -9897,7 +9981,7 @@
       <c r="AI208" s="4"/>
       <c r="AJ208" s="4"/>
     </row>
-    <row r="209" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -9935,7 +10019,7 @@
       <c r="AI209" s="4"/>
       <c r="AJ209" s="4"/>
     </row>
-    <row r="210" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -9973,7 +10057,7 @@
       <c r="AI210" s="4"/>
       <c r="AJ210" s="4"/>
     </row>
-    <row r="211" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -10011,7 +10095,7 @@
       <c r="AI211" s="4"/>
       <c r="AJ211" s="4"/>
     </row>
-    <row r="212" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -10049,7 +10133,7 @@
       <c r="AI212" s="4"/>
       <c r="AJ212" s="4"/>
     </row>
-    <row r="213" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -10087,7 +10171,7 @@
       <c r="AI213" s="4"/>
       <c r="AJ213" s="4"/>
     </row>
-    <row r="214" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -10125,7 +10209,7 @@
       <c r="AI214" s="4"/>
       <c r="AJ214" s="4"/>
     </row>
-    <row r="215" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -10163,7 +10247,7 @@
       <c r="AI215" s="4"/>
       <c r="AJ215" s="4"/>
     </row>
-    <row r="216" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -10201,7 +10285,7 @@
       <c r="AI216" s="4"/>
       <c r="AJ216" s="4"/>
     </row>
-    <row r="217" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -10239,7 +10323,7 @@
       <c r="AI217" s="4"/>
       <c r="AJ217" s="4"/>
     </row>
-    <row r="218" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -10277,7 +10361,7 @@
       <c r="AI218" s="4"/>
       <c r="AJ218" s="4"/>
     </row>
-    <row r="219" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -10315,7 +10399,7 @@
       <c r="AI219" s="4"/>
       <c r="AJ219" s="4"/>
     </row>
-    <row r="220" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -10353,7 +10437,7 @@
       <c r="AI220" s="4"/>
       <c r="AJ220" s="4"/>
     </row>
-    <row r="221" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
@@ -10391,7 +10475,7 @@
       <c r="AI221" s="4"/>
       <c r="AJ221" s="4"/>
     </row>
-    <row r="222" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A222" s="4"/>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
@@ -10429,7 +10513,7 @@
       <c r="AI222" s="4"/>
       <c r="AJ222" s="4"/>
     </row>
-    <row r="223" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
@@ -10467,7 +10551,7 @@
       <c r="AI223" s="4"/>
       <c r="AJ223" s="4"/>
     </row>
-    <row r="224" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
@@ -10505,7 +10589,7 @@
       <c r="AI224" s="4"/>
       <c r="AJ224" s="4"/>
     </row>
-    <row r="225" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A225" s="4"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
@@ -10543,7 +10627,7 @@
       <c r="AI225" s="4"/>
       <c r="AJ225" s="4"/>
     </row>
-    <row r="226" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
@@ -10581,7 +10665,7 @@
       <c r="AI226" s="4"/>
       <c r="AJ226" s="4"/>
     </row>
-    <row r="227" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
@@ -10619,7 +10703,7 @@
       <c r="AI227" s="4"/>
       <c r="AJ227" s="4"/>
     </row>
-    <row r="228" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
@@ -10657,7 +10741,7 @@
       <c r="AI228" s="4"/>
       <c r="AJ228" s="4"/>
     </row>
-    <row r="229" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
@@ -10695,7 +10779,7 @@
       <c r="AI229" s="4"/>
       <c r="AJ229" s="4"/>
     </row>
-    <row r="230" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
@@ -10733,7 +10817,7 @@
       <c r="AI230" s="4"/>
       <c r="AJ230" s="4"/>
     </row>
-    <row r="231" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
@@ -10771,7 +10855,7 @@
       <c r="AI231" s="4"/>
       <c r="AJ231" s="4"/>
     </row>
-    <row r="232" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -10809,7 +10893,7 @@
       <c r="AI232" s="4"/>
       <c r="AJ232" s="4"/>
     </row>
-    <row r="233" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
@@ -10847,7 +10931,7 @@
       <c r="AI233" s="4"/>
       <c r="AJ233" s="4"/>
     </row>
-    <row r="234" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
@@ -10885,7 +10969,7 @@
       <c r="AI234" s="4"/>
       <c r="AJ234" s="4"/>
     </row>
-    <row r="235" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
@@ -10923,7 +11007,7 @@
       <c r="AI235" s="4"/>
       <c r="AJ235" s="4"/>
     </row>
-    <row r="236" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -10961,7 +11045,7 @@
       <c r="AI236" s="4"/>
       <c r="AJ236" s="4"/>
     </row>
-    <row r="237" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
@@ -10999,7 +11083,7 @@
       <c r="AI237" s="4"/>
       <c r="AJ237" s="4"/>
     </row>
-    <row r="238" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -11037,7 +11121,7 @@
       <c r="AI238" s="4"/>
       <c r="AJ238" s="4"/>
     </row>
-    <row r="239" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -11075,7 +11159,7 @@
       <c r="AI239" s="4"/>
       <c r="AJ239" s="4"/>
     </row>
-    <row r="240" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -11113,7 +11197,7 @@
       <c r="AI240" s="4"/>
       <c r="AJ240" s="4"/>
     </row>
-    <row r="241" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
@@ -11151,7 +11235,7 @@
       <c r="AI241" s="4"/>
       <c r="AJ241" s="4"/>
     </row>
-    <row r="242" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
@@ -11189,7 +11273,7 @@
       <c r="AI242" s="4"/>
       <c r="AJ242" s="4"/>
     </row>
-    <row r="243" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A243" s="4"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
@@ -11227,7 +11311,7 @@
       <c r="AI243" s="4"/>
       <c r="AJ243" s="4"/>
     </row>
-    <row r="244" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -11265,7 +11349,7 @@
       <c r="AI244" s="4"/>
       <c r="AJ244" s="4"/>
     </row>
-    <row r="245" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A245" s="4"/>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -11303,7 +11387,7 @@
       <c r="AI245" s="4"/>
       <c r="AJ245" s="4"/>
     </row>
-    <row r="246" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A246" s="4"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -11341,7 +11425,7 @@
       <c r="AI246" s="4"/>
       <c r="AJ246" s="4"/>
     </row>
-    <row r="247" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -11379,7 +11463,7 @@
       <c r="AI247" s="4"/>
       <c r="AJ247" s="4"/>
     </row>
-    <row r="248" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -11417,7 +11501,7 @@
       <c r="AI248" s="4"/>
       <c r="AJ248" s="4"/>
     </row>
-    <row r="249" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
@@ -11455,7 +11539,7 @@
       <c r="AI249" s="4"/>
       <c r="AJ249" s="4"/>
     </row>
-    <row r="250" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
@@ -11493,7 +11577,7 @@
       <c r="AI250" s="4"/>
       <c r="AJ250" s="4"/>
     </row>
-    <row r="251" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -11531,7 +11615,7 @@
       <c r="AI251" s="4"/>
       <c r="AJ251" s="4"/>
     </row>
-    <row r="252" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -11569,7 +11653,7 @@
       <c r="AI252" s="4"/>
       <c r="AJ252" s="4"/>
     </row>
-    <row r="253" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A253" s="4"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -11607,7 +11691,7 @@
       <c r="AI253" s="4"/>
       <c r="AJ253" s="4"/>
     </row>
-    <row r="254" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A254" s="4"/>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -11645,7 +11729,7 @@
       <c r="AI254" s="4"/>
       <c r="AJ254" s="4"/>
     </row>
-    <row r="255" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A255" s="4"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
@@ -11683,7 +11767,7 @@
       <c r="AI255" s="4"/>
       <c r="AJ255" s="4"/>
     </row>
-    <row r="256" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -11721,7 +11805,7 @@
       <c r="AI256" s="4"/>
       <c r="AJ256" s="4"/>
     </row>
-    <row r="257" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -11759,7 +11843,7 @@
       <c r="AI257" s="4"/>
       <c r="AJ257" s="4"/>
     </row>
-    <row r="258" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A258" s="4"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -11797,7 +11881,7 @@
       <c r="AI258" s="4"/>
       <c r="AJ258" s="4"/>
     </row>
-    <row r="259" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
@@ -11835,7 +11919,7 @@
       <c r="AI259" s="4"/>
       <c r="AJ259" s="4"/>
     </row>
-    <row r="260" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
@@ -11873,7 +11957,7 @@
       <c r="AI260" s="4"/>
       <c r="AJ260" s="4"/>
     </row>
-    <row r="261" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A261" s="4"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -11911,7 +11995,7 @@
       <c r="AI261" s="4"/>
       <c r="AJ261" s="4"/>
     </row>
-    <row r="262" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
@@ -11949,7 +12033,7 @@
       <c r="AI262" s="4"/>
       <c r="AJ262" s="4"/>
     </row>
-    <row r="263" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A263" s="4"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
@@ -11987,7 +12071,7 @@
       <c r="AI263" s="4"/>
       <c r="AJ263" s="4"/>
     </row>
-    <row r="264" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -12025,7 +12109,7 @@
       <c r="AI264" s="4"/>
       <c r="AJ264" s="4"/>
     </row>
-    <row r="265" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A265" s="4"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -12063,7 +12147,7 @@
       <c r="AI265" s="4"/>
       <c r="AJ265" s="4"/>
     </row>
-    <row r="266" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
@@ -12101,7 +12185,7 @@
       <c r="AI266" s="4"/>
       <c r="AJ266" s="4"/>
     </row>
-    <row r="267" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -12139,7 +12223,7 @@
       <c r="AI267" s="4"/>
       <c r="AJ267" s="4"/>
     </row>
-    <row r="268" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -12177,7 +12261,7 @@
       <c r="AI268" s="4"/>
       <c r="AJ268" s="4"/>
     </row>
-    <row r="269" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
@@ -12215,7 +12299,7 @@
       <c r="AI269" s="4"/>
       <c r="AJ269" s="4"/>
     </row>
-    <row r="270" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -12253,7 +12337,7 @@
       <c r="AI270" s="4"/>
       <c r="AJ270" s="4"/>
     </row>
-    <row r="271" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
@@ -12291,7 +12375,7 @@
       <c r="AI271" s="4"/>
       <c r="AJ271" s="4"/>
     </row>
-    <row r="272" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
@@ -12329,7 +12413,7 @@
       <c r="AI272" s="4"/>
       <c r="AJ272" s="4"/>
     </row>
-    <row r="273" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A273" s="4"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -12367,7 +12451,7 @@
       <c r="AI273" s="4"/>
       <c r="AJ273" s="4"/>
     </row>
-    <row r="274" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
@@ -12405,7 +12489,7 @@
       <c r="AI274" s="4"/>
       <c r="AJ274" s="4"/>
     </row>
-    <row r="275" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
@@ -12443,7 +12527,7 @@
       <c r="AI275" s="4"/>
       <c r="AJ275" s="4"/>
     </row>
-    <row r="276" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -12481,7 +12565,7 @@
       <c r="AI276" s="4"/>
       <c r="AJ276" s="4"/>
     </row>
-    <row r="277" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
@@ -12519,7 +12603,7 @@
       <c r="AI277" s="4"/>
       <c r="AJ277" s="4"/>
     </row>
-    <row r="278" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
@@ -12557,7 +12641,7 @@
       <c r="AI278" s="4"/>
       <c r="AJ278" s="4"/>
     </row>
-    <row r="279" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
@@ -12595,7 +12679,7 @@
       <c r="AI279" s="4"/>
       <c r="AJ279" s="4"/>
     </row>
-    <row r="280" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
@@ -12633,7 +12717,7 @@
       <c r="AI280" s="4"/>
       <c r="AJ280" s="4"/>
     </row>
-    <row r="281" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A281" s="4"/>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
@@ -12671,7 +12755,7 @@
       <c r="AI281" s="4"/>
       <c r="AJ281" s="4"/>
     </row>
-    <row r="282" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
@@ -12709,7 +12793,7 @@
       <c r="AI282" s="4"/>
       <c r="AJ282" s="4"/>
     </row>
-    <row r="283" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A283" s="4"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
@@ -12747,7 +12831,7 @@
       <c r="AI283" s="4"/>
       <c r="AJ283" s="4"/>
     </row>
-    <row r="284" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
@@ -12785,7 +12869,7 @@
       <c r="AI284" s="4"/>
       <c r="AJ284" s="4"/>
     </row>
-    <row r="285" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A285" s="4"/>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
@@ -12823,7 +12907,7 @@
       <c r="AI285" s="4"/>
       <c r="AJ285" s="4"/>
     </row>
-    <row r="286" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
@@ -12861,7 +12945,7 @@
       <c r="AI286" s="4"/>
       <c r="AJ286" s="4"/>
     </row>
-    <row r="287" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
@@ -12899,7 +12983,7 @@
       <c r="AI287" s="4"/>
       <c r="AJ287" s="4"/>
     </row>
-    <row r="288" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
@@ -12937,7 +13021,7 @@
       <c r="AI288" s="4"/>
       <c r="AJ288" s="4"/>
     </row>
-    <row r="289" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
@@ -12975,7 +13059,7 @@
       <c r="AI289" s="4"/>
       <c r="AJ289" s="4"/>
     </row>
-    <row r="290" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
@@ -13013,7 +13097,7 @@
       <c r="AI290" s="4"/>
       <c r="AJ290" s="4"/>
     </row>
-    <row r="291" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
@@ -13051,7 +13135,7 @@
       <c r="AI291" s="4"/>
       <c r="AJ291" s="4"/>
     </row>
-    <row r="292" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
@@ -13089,7 +13173,7 @@
       <c r="AI292" s="4"/>
       <c r="AJ292" s="4"/>
     </row>
-    <row r="293" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A293" s="4"/>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
@@ -13127,7 +13211,7 @@
       <c r="AI293" s="4"/>
       <c r="AJ293" s="4"/>
     </row>
-    <row r="294" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -13165,7 +13249,7 @@
       <c r="AI294" s="4"/>
       <c r="AJ294" s="4"/>
     </row>
-    <row r="295" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A295" s="4"/>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
@@ -13203,7 +13287,7 @@
       <c r="AI295" s="4"/>
       <c r="AJ295" s="4"/>
     </row>
-    <row r="296" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
@@ -13241,7 +13325,7 @@
       <c r="AI296" s="4"/>
       <c r="AJ296" s="4"/>
     </row>
-    <row r="297" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
@@ -13279,7 +13363,7 @@
       <c r="AI297" s="4"/>
       <c r="AJ297" s="4"/>
     </row>
-    <row r="298" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A298" s="4"/>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
@@ -13317,7 +13401,7 @@
       <c r="AI298" s="4"/>
       <c r="AJ298" s="4"/>
     </row>
-    <row r="299" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A299" s="4"/>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
@@ -13355,7 +13439,7 @@
       <c r="AI299" s="4"/>
       <c r="AJ299" s="4"/>
     </row>
-    <row r="300" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -13393,7 +13477,7 @@
       <c r="AI300" s="4"/>
       <c r="AJ300" s="4"/>
     </row>
-    <row r="301" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
@@ -13431,7 +13515,7 @@
       <c r="AI301" s="4"/>
       <c r="AJ301" s="4"/>
     </row>
-    <row r="302" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
@@ -13469,7 +13553,7 @@
       <c r="AI302" s="4"/>
       <c r="AJ302" s="4"/>
     </row>
-    <row r="303" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
@@ -13507,7 +13591,7 @@
       <c r="AI303" s="4"/>
       <c r="AJ303" s="4"/>
     </row>
-    <row r="304" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
@@ -13545,7 +13629,7 @@
       <c r="AI304" s="4"/>
       <c r="AJ304" s="4"/>
     </row>
-    <row r="305" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
@@ -13583,7 +13667,7 @@
       <c r="AI305" s="4"/>
       <c r="AJ305" s="4"/>
     </row>
-    <row r="306" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
@@ -13621,7 +13705,7 @@
       <c r="AI306" s="4"/>
       <c r="AJ306" s="4"/>
     </row>
-    <row r="307" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
@@ -13659,7 +13743,7 @@
       <c r="AI307" s="4"/>
       <c r="AJ307" s="4"/>
     </row>
-    <row r="308" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
@@ -13697,7 +13781,7 @@
       <c r="AI308" s="4"/>
       <c r="AJ308" s="4"/>
     </row>
-    <row r="309" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
@@ -13735,7 +13819,7 @@
       <c r="AI309" s="4"/>
       <c r="AJ309" s="4"/>
     </row>
-    <row r="310" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
@@ -13773,7 +13857,7 @@
       <c r="AI310" s="4"/>
       <c r="AJ310" s="4"/>
     </row>
-    <row r="311" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
@@ -13811,7 +13895,7 @@
       <c r="AI311" s="4"/>
       <c r="AJ311" s="4"/>
     </row>
-    <row r="312" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
@@ -13849,7 +13933,7 @@
       <c r="AI312" s="4"/>
       <c r="AJ312" s="4"/>
     </row>
-    <row r="313" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
@@ -13887,7 +13971,7 @@
       <c r="AI313" s="4"/>
       <c r="AJ313" s="4"/>
     </row>
-    <row r="314" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
@@ -13925,7 +14009,7 @@
       <c r="AI314" s="4"/>
       <c r="AJ314" s="4"/>
     </row>
-    <row r="315" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
@@ -13963,7 +14047,7 @@
       <c r="AI315" s="4"/>
       <c r="AJ315" s="4"/>
     </row>
-    <row r="316" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
@@ -14001,7 +14085,7 @@
       <c r="AI316" s="4"/>
       <c r="AJ316" s="4"/>
     </row>
-    <row r="317" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
@@ -14039,7 +14123,7 @@
       <c r="AI317" s="4"/>
       <c r="AJ317" s="4"/>
     </row>
-    <row r="318" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
@@ -14077,7 +14161,7 @@
       <c r="AI318" s="4"/>
       <c r="AJ318" s="4"/>
     </row>
-    <row r="319" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
@@ -14115,7 +14199,7 @@
       <c r="AI319" s="4"/>
       <c r="AJ319" s="4"/>
     </row>
-    <row r="320" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
@@ -14153,7 +14237,7 @@
       <c r="AI320" s="4"/>
       <c r="AJ320" s="4"/>
     </row>
-    <row r="321" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
@@ -14191,7 +14275,7 @@
       <c r="AI321" s="4"/>
       <c r="AJ321" s="4"/>
     </row>
-    <row r="322" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A322" s="4"/>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
@@ -14229,7 +14313,7 @@
       <c r="AI322" s="4"/>
       <c r="AJ322" s="4"/>
     </row>
-    <row r="323" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A323" s="4"/>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
@@ -14267,7 +14351,7 @@
       <c r="AI323" s="4"/>
       <c r="AJ323" s="4"/>
     </row>
-    <row r="324" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
@@ -14305,7 +14389,7 @@
       <c r="AI324" s="4"/>
       <c r="AJ324" s="4"/>
     </row>
-    <row r="325" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
@@ -14343,7 +14427,7 @@
       <c r="AI325" s="4"/>
       <c r="AJ325" s="4"/>
     </row>
-    <row r="326" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
@@ -14381,7 +14465,7 @@
       <c r="AI326" s="4"/>
       <c r="AJ326" s="4"/>
     </row>
-    <row r="327" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -14419,7 +14503,7 @@
       <c r="AI327" s="4"/>
       <c r="AJ327" s="4"/>
     </row>
-    <row r="328" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
@@ -14457,7 +14541,7 @@
       <c r="AI328" s="4"/>
       <c r="AJ328" s="4"/>
     </row>
-    <row r="329" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
@@ -14495,7 +14579,7 @@
       <c r="AI329" s="4"/>
       <c r="AJ329" s="4"/>
     </row>
-    <row r="330" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
@@ -14533,7 +14617,7 @@
       <c r="AI330" s="4"/>
       <c r="AJ330" s="4"/>
     </row>
-    <row r="331" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
@@ -14571,7 +14655,7 @@
       <c r="AI331" s="4"/>
       <c r="AJ331" s="4"/>
     </row>
-    <row r="332" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
@@ -14609,7 +14693,7 @@
       <c r="AI332" s="4"/>
       <c r="AJ332" s="4"/>
     </row>
-    <row r="333" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
@@ -14647,7 +14731,7 @@
       <c r="AI333" s="4"/>
       <c r="AJ333" s="4"/>
     </row>
-    <row r="334" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A334" s="4"/>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
@@ -14685,7 +14769,7 @@
       <c r="AI334" s="4"/>
       <c r="AJ334" s="4"/>
     </row>
-    <row r="335" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A335" s="4"/>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -14723,7 +14807,7 @@
       <c r="AI335" s="4"/>
       <c r="AJ335" s="4"/>
     </row>
-    <row r="336" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -14761,7 +14845,7 @@
       <c r="AI336" s="4"/>
       <c r="AJ336" s="4"/>
     </row>
-    <row r="337" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -14799,7 +14883,7 @@
       <c r="AI337" s="4"/>
       <c r="AJ337" s="4"/>
     </row>
-    <row r="338" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -14837,7 +14921,7 @@
       <c r="AI338" s="4"/>
       <c r="AJ338" s="4"/>
     </row>
-    <row r="339" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -14875,7 +14959,7 @@
       <c r="AI339" s="4"/>
       <c r="AJ339" s="4"/>
     </row>
-    <row r="340" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -14913,7 +14997,7 @@
       <c r="AI340" s="4"/>
       <c r="AJ340" s="4"/>
     </row>
-    <row r="341" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -14951,7 +15035,7 @@
       <c r="AI341" s="4"/>
       <c r="AJ341" s="4"/>
     </row>
-    <row r="342" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -14989,7 +15073,7 @@
       <c r="AI342" s="4"/>
       <c r="AJ342" s="4"/>
     </row>
-    <row r="343" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A343" s="4"/>
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
@@ -15027,7 +15111,7 @@
       <c r="AI343" s="4"/>
       <c r="AJ343" s="4"/>
     </row>
-    <row r="344" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
@@ -15065,7 +15149,7 @@
       <c r="AI344" s="4"/>
       <c r="AJ344" s="4"/>
     </row>
-    <row r="345" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
@@ -15103,7 +15187,7 @@
       <c r="AI345" s="4"/>
       <c r="AJ345" s="4"/>
     </row>
-    <row r="346" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A346" s="4"/>
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
@@ -15141,7 +15225,7 @@
       <c r="AI346" s="4"/>
       <c r="AJ346" s="4"/>
     </row>
-    <row r="347" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A347" s="4"/>
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
@@ -15179,7 +15263,7 @@
       <c r="AI347" s="4"/>
       <c r="AJ347" s="4"/>
     </row>
-    <row r="348" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
@@ -15217,7 +15301,7 @@
       <c r="AI348" s="4"/>
       <c r="AJ348" s="4"/>
     </row>
-    <row r="349" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A349" s="4"/>
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
@@ -15255,7 +15339,7 @@
       <c r="AI349" s="4"/>
       <c r="AJ349" s="4"/>
     </row>
-    <row r="350" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
@@ -15293,7 +15377,7 @@
       <c r="AI350" s="4"/>
       <c r="AJ350" s="4"/>
     </row>
-    <row r="351" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
@@ -15331,7 +15415,7 @@
       <c r="AI351" s="4"/>
       <c r="AJ351" s="4"/>
     </row>
-    <row r="352" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
@@ -15369,7 +15453,7 @@
       <c r="AI352" s="4"/>
       <c r="AJ352" s="4"/>
     </row>
-    <row r="353" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
@@ -15407,7 +15491,7 @@
       <c r="AI353" s="4"/>
       <c r="AJ353" s="4"/>
     </row>
-    <row r="354" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
@@ -15445,7 +15529,7 @@
       <c r="AI354" s="4"/>
       <c r="AJ354" s="4"/>
     </row>
-    <row r="355" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
@@ -15483,7 +15567,7 @@
       <c r="AI355" s="4"/>
       <c r="AJ355" s="4"/>
     </row>
-    <row r="356" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A356" s="4"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
@@ -15521,7 +15605,7 @@
       <c r="AI356" s="4"/>
       <c r="AJ356" s="4"/>
     </row>
-    <row r="357" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
@@ -15559,7 +15643,7 @@
       <c r="AI357" s="4"/>
       <c r="AJ357" s="4"/>
     </row>
-    <row r="358" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
@@ -15597,7 +15681,7 @@
       <c r="AI358" s="4"/>
       <c r="AJ358" s="4"/>
     </row>
-    <row r="359" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
@@ -15635,7 +15719,7 @@
       <c r="AI359" s="4"/>
       <c r="AJ359" s="4"/>
     </row>
-    <row r="360" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A360" s="4"/>
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
@@ -15673,7 +15757,7 @@
       <c r="AI360" s="4"/>
       <c r="AJ360" s="4"/>
     </row>
-    <row r="361" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A361" s="4"/>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
@@ -15711,7 +15795,7 @@
       <c r="AI361" s="4"/>
       <c r="AJ361" s="4"/>
     </row>
-    <row r="362" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A362" s="4"/>
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
@@ -15749,7 +15833,7 @@
       <c r="AI362" s="4"/>
       <c r="AJ362" s="4"/>
     </row>
-    <row r="363" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A363" s="4"/>
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
@@ -15787,7 +15871,7 @@
       <c r="AI363" s="4"/>
       <c r="AJ363" s="4"/>
     </row>
-    <row r="364" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
@@ -15825,7 +15909,7 @@
       <c r="AI364" s="4"/>
       <c r="AJ364" s="4"/>
     </row>
-    <row r="365" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
@@ -15863,7 +15947,7 @@
       <c r="AI365" s="4"/>
       <c r="AJ365" s="4"/>
     </row>
-    <row r="366" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
@@ -15901,7 +15985,7 @@
       <c r="AI366" s="4"/>
       <c r="AJ366" s="4"/>
     </row>
-    <row r="367" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A367" s="4"/>
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
@@ -15939,7 +16023,7 @@
       <c r="AI367" s="4"/>
       <c r="AJ367" s="4"/>
     </row>
-    <row r="368" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A368" s="4"/>
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
@@ -15977,7 +16061,7 @@
       <c r="AI368" s="4"/>
       <c r="AJ368" s="4"/>
     </row>
-    <row r="369" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A369" s="4"/>
       <c r="B369" s="4"/>
       <c r="C369" s="4"/>
@@ -16015,7 +16099,7 @@
       <c r="AI369" s="4"/>
       <c r="AJ369" s="4"/>
     </row>
-    <row r="370" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A370" s="4"/>
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
@@ -16053,7 +16137,7 @@
       <c r="AI370" s="4"/>
       <c r="AJ370" s="4"/>
     </row>
-    <row r="371" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A371" s="4"/>
       <c r="B371" s="4"/>
       <c r="C371" s="4"/>
@@ -16091,7 +16175,7 @@
       <c r="AI371" s="4"/>
       <c r="AJ371" s="4"/>
     </row>
-    <row r="372" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A372" s="4"/>
       <c r="B372" s="4"/>
       <c r="C372" s="4"/>
@@ -16129,7 +16213,7 @@
       <c r="AI372" s="4"/>
       <c r="AJ372" s="4"/>
     </row>
-    <row r="373" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A373" s="4"/>
       <c r="B373" s="4"/>
       <c r="C373" s="4"/>
@@ -16167,7 +16251,7 @@
       <c r="AI373" s="4"/>
       <c r="AJ373" s="4"/>
     </row>
-    <row r="374" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A374" s="4"/>
       <c r="B374" s="4"/>
       <c r="C374" s="4"/>
@@ -16205,7 +16289,7 @@
       <c r="AI374" s="4"/>
       <c r="AJ374" s="4"/>
     </row>
-    <row r="375" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A375" s="4"/>
       <c r="B375" s="4"/>
       <c r="C375" s="4"/>
@@ -16243,7 +16327,7 @@
       <c r="AI375" s="4"/>
       <c r="AJ375" s="4"/>
     </row>
-    <row r="376" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
@@ -16281,7 +16365,7 @@
       <c r="AI376" s="4"/>
       <c r="AJ376" s="4"/>
     </row>
-    <row r="377" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
@@ -16319,7 +16403,7 @@
       <c r="AI377" s="4"/>
       <c r="AJ377" s="4"/>
     </row>
-    <row r="378" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A378" s="4"/>
       <c r="B378" s="4"/>
       <c r="C378" s="4"/>
@@ -16357,7 +16441,7 @@
       <c r="AI378" s="4"/>
       <c r="AJ378" s="4"/>
     </row>
-    <row r="379" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
@@ -16395,7 +16479,7 @@
       <c r="AI379" s="4"/>
       <c r="AJ379" s="4"/>
     </row>
-    <row r="380" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
@@ -16433,7 +16517,7 @@
       <c r="AI380" s="4"/>
       <c r="AJ380" s="4"/>
     </row>
-    <row r="381" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A381" s="4"/>
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
@@ -16471,7 +16555,7 @@
       <c r="AI381" s="4"/>
       <c r="AJ381" s="4"/>
     </row>
-    <row r="382" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A382" s="4"/>
       <c r="B382" s="4"/>
       <c r="C382" s="4"/>
@@ -16509,7 +16593,7 @@
       <c r="AI382" s="4"/>
       <c r="AJ382" s="4"/>
     </row>
-    <row r="383" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A383" s="4"/>
       <c r="B383" s="4"/>
       <c r="C383" s="4"/>
@@ -16547,7 +16631,7 @@
       <c r="AI383" s="4"/>
       <c r="AJ383" s="4"/>
     </row>
-    <row r="384" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
@@ -16585,7 +16669,7 @@
       <c r="AI384" s="4"/>
       <c r="AJ384" s="4"/>
     </row>
-    <row r="385" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A385" s="4"/>
       <c r="B385" s="4"/>
       <c r="C385" s="4"/>
@@ -16623,7 +16707,7 @@
       <c r="AI385" s="4"/>
       <c r="AJ385" s="4"/>
     </row>
-    <row r="386" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A386" s="4"/>
       <c r="B386" s="4"/>
       <c r="C386" s="4"/>
@@ -16661,7 +16745,7 @@
       <c r="AI386" s="4"/>
       <c r="AJ386" s="4"/>
     </row>
-    <row r="387" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A387" s="4"/>
       <c r="B387" s="4"/>
       <c r="C387" s="4"/>
@@ -16699,7 +16783,7 @@
       <c r="AI387" s="4"/>
       <c r="AJ387" s="4"/>
     </row>
-    <row r="388" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A388" s="4"/>
       <c r="B388" s="4"/>
       <c r="C388" s="4"/>
@@ -16737,7 +16821,7 @@
       <c r="AI388" s="4"/>
       <c r="AJ388" s="4"/>
     </row>
-    <row r="389" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A389" s="4"/>
       <c r="B389" s="4"/>
       <c r="C389" s="4"/>
@@ -16775,7 +16859,7 @@
       <c r="AI389" s="4"/>
       <c r="AJ389" s="4"/>
     </row>
-    <row r="390" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A390" s="4"/>
       <c r="B390" s="4"/>
       <c r="C390" s="4"/>
@@ -16813,7 +16897,7 @@
       <c r="AI390" s="4"/>
       <c r="AJ390" s="4"/>
     </row>
-    <row r="391" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A391" s="4"/>
       <c r="B391" s="4"/>
       <c r="C391" s="4"/>
@@ -16851,7 +16935,7 @@
       <c r="AI391" s="4"/>
       <c r="AJ391" s="4"/>
     </row>
-    <row r="392" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A392" s="4"/>
       <c r="B392" s="4"/>
       <c r="C392" s="4"/>
@@ -16889,7 +16973,7 @@
       <c r="AI392" s="4"/>
       <c r="AJ392" s="4"/>
     </row>
-    <row r="393" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
@@ -16927,7 +17011,7 @@
       <c r="AI393" s="4"/>
       <c r="AJ393" s="4"/>
     </row>
-    <row r="394" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
@@ -16965,7 +17049,7 @@
       <c r="AI394" s="4"/>
       <c r="AJ394" s="4"/>
     </row>
-    <row r="395" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A395" s="4"/>
       <c r="B395" s="4"/>
       <c r="C395" s="4"/>
@@ -17003,7 +17087,7 @@
       <c r="AI395" s="4"/>
       <c r="AJ395" s="4"/>
     </row>
-    <row r="396" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
@@ -17041,7 +17125,7 @@
       <c r="AI396" s="4"/>
       <c r="AJ396" s="4"/>
     </row>
-    <row r="397" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
@@ -17079,7 +17163,7 @@
       <c r="AI397" s="4"/>
       <c r="AJ397" s="4"/>
     </row>
-    <row r="398" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A398" s="4"/>
       <c r="B398" s="4"/>
       <c r="C398" s="4"/>
@@ -17117,7 +17201,7 @@
       <c r="AI398" s="4"/>
       <c r="AJ398" s="4"/>
     </row>
-    <row r="399" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A399" s="4"/>
       <c r="B399" s="4"/>
       <c r="C399" s="4"/>
@@ -17155,7 +17239,7 @@
       <c r="AI399" s="4"/>
       <c r="AJ399" s="4"/>
     </row>
-    <row r="400" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A400" s="4"/>
       <c r="B400" s="4"/>
       <c r="C400" s="4"/>
@@ -17193,7 +17277,7 @@
       <c r="AI400" s="4"/>
       <c r="AJ400" s="4"/>
     </row>
-    <row r="401" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
@@ -17231,7 +17315,7 @@
       <c r="AI401" s="4"/>
       <c r="AJ401" s="4"/>
     </row>
-    <row r="402" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A402" s="4"/>
       <c r="B402" s="4"/>
       <c r="C402" s="4"/>
@@ -17269,7 +17353,7 @@
       <c r="AI402" s="4"/>
       <c r="AJ402" s="4"/>
     </row>
-    <row r="403" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A403" s="4"/>
       <c r="B403" s="4"/>
       <c r="C403" s="4"/>
@@ -17307,7 +17391,7 @@
       <c r="AI403" s="4"/>
       <c r="AJ403" s="4"/>
     </row>
-    <row r="404" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A404" s="4"/>
       <c r="B404" s="4"/>
       <c r="C404" s="4"/>
@@ -17345,7 +17429,7 @@
       <c r="AI404" s="4"/>
       <c r="AJ404" s="4"/>
     </row>
-    <row r="405" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A405" s="4"/>
       <c r="B405" s="4"/>
       <c r="C405" s="4"/>
@@ -17383,7 +17467,7 @@
       <c r="AI405" s="4"/>
       <c r="AJ405" s="4"/>
     </row>
-    <row r="406" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A406" s="4"/>
       <c r="B406" s="4"/>
       <c r="C406" s="4"/>
@@ -17421,7 +17505,7 @@
       <c r="AI406" s="4"/>
       <c r="AJ406" s="4"/>
     </row>
-    <row r="407" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A407" s="4"/>
       <c r="B407" s="4"/>
       <c r="C407" s="4"/>
@@ -17459,7 +17543,7 @@
       <c r="AI407" s="4"/>
       <c r="AJ407" s="4"/>
     </row>
-    <row r="408" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A408" s="4"/>
       <c r="B408" s="4"/>
       <c r="C408" s="4"/>
@@ -17497,7 +17581,7 @@
       <c r="AI408" s="4"/>
       <c r="AJ408" s="4"/>
     </row>
-    <row r="409" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A409" s="4"/>
       <c r="B409" s="4"/>
       <c r="C409" s="4"/>
@@ -17535,7 +17619,7 @@
       <c r="AI409" s="4"/>
       <c r="AJ409" s="4"/>
     </row>
-    <row r="410" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A410" s="4"/>
       <c r="B410" s="4"/>
       <c r="C410" s="4"/>
@@ -17573,7 +17657,7 @@
       <c r="AI410" s="4"/>
       <c r="AJ410" s="4"/>
     </row>
-    <row r="411" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A411" s="4"/>
       <c r="B411" s="4"/>
       <c r="C411" s="4"/>
@@ -17611,7 +17695,7 @@
       <c r="AI411" s="4"/>
       <c r="AJ411" s="4"/>
     </row>
-    <row r="412" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A412" s="4"/>
       <c r="B412" s="4"/>
       <c r="C412" s="4"/>
@@ -17649,7 +17733,7 @@
       <c r="AI412" s="4"/>
       <c r="AJ412" s="4"/>
     </row>
-    <row r="413" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A413" s="4"/>
       <c r="B413" s="4"/>
       <c r="C413" s="4"/>
@@ -17687,7 +17771,7 @@
       <c r="AI413" s="4"/>
       <c r="AJ413" s="4"/>
     </row>
-    <row r="414" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A414" s="4"/>
       <c r="B414" s="4"/>
       <c r="C414" s="4"/>
@@ -17725,7 +17809,7 @@
       <c r="AI414" s="4"/>
       <c r="AJ414" s="4"/>
     </row>
-    <row r="415" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A415" s="4"/>
       <c r="B415" s="4"/>
       <c r="C415" s="4"/>
@@ -17763,7 +17847,7 @@
       <c r="AI415" s="4"/>
       <c r="AJ415" s="4"/>
     </row>
-    <row r="416" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A416" s="4"/>
       <c r="B416" s="4"/>
       <c r="C416" s="4"/>
@@ -17801,7 +17885,7 @@
       <c r="AI416" s="4"/>
       <c r="AJ416" s="4"/>
     </row>
-    <row r="417" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A417" s="4"/>
       <c r="B417" s="4"/>
       <c r="C417" s="4"/>
@@ -17839,7 +17923,7 @@
       <c r="AI417" s="4"/>
       <c r="AJ417" s="4"/>
     </row>
-    <row r="418" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A418" s="4"/>
       <c r="B418" s="4"/>
       <c r="C418" s="4"/>
@@ -17877,7 +17961,7 @@
       <c r="AI418" s="4"/>
       <c r="AJ418" s="4"/>
     </row>
-    <row r="419" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A419" s="4"/>
       <c r="B419" s="4"/>
       <c r="C419" s="4"/>
@@ -17915,7 +17999,7 @@
       <c r="AI419" s="4"/>
       <c r="AJ419" s="4"/>
     </row>
-    <row r="420" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A420" s="4"/>
       <c r="B420" s="4"/>
       <c r="C420" s="4"/>
@@ -17953,7 +18037,7 @@
       <c r="AI420" s="4"/>
       <c r="AJ420" s="4"/>
     </row>
-    <row r="421" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A421" s="4"/>
       <c r="B421" s="4"/>
       <c r="C421" s="4"/>
@@ -17991,7 +18075,7 @@
       <c r="AI421" s="4"/>
       <c r="AJ421" s="4"/>
     </row>
-    <row r="422" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A422" s="4"/>
       <c r="B422" s="4"/>
       <c r="C422" s="4"/>
@@ -18029,7 +18113,7 @@
       <c r="AI422" s="4"/>
       <c r="AJ422" s="4"/>
     </row>
-    <row r="423" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A423" s="4"/>
       <c r="B423" s="4"/>
       <c r="C423" s="4"/>
@@ -18067,7 +18151,7 @@
       <c r="AI423" s="4"/>
       <c r="AJ423" s="4"/>
     </row>
-    <row r="424" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A424" s="4"/>
       <c r="B424" s="4"/>
       <c r="C424" s="4"/>
@@ -18105,7 +18189,7 @@
       <c r="AI424" s="4"/>
       <c r="AJ424" s="4"/>
     </row>
-    <row r="425" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A425" s="4"/>
       <c r="B425" s="4"/>
       <c r="C425" s="4"/>
@@ -18143,7 +18227,7 @@
       <c r="AI425" s="4"/>
       <c r="AJ425" s="4"/>
     </row>
-    <row r="426" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A426" s="4"/>
       <c r="B426" s="4"/>
       <c r="C426" s="4"/>
@@ -18181,7 +18265,7 @@
       <c r="AI426" s="4"/>
       <c r="AJ426" s="4"/>
     </row>
-    <row r="427" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A427" s="4"/>
       <c r="B427" s="4"/>
       <c r="C427" s="4"/>
@@ -18219,7 +18303,7 @@
       <c r="AI427" s="4"/>
       <c r="AJ427" s="4"/>
     </row>
-    <row r="428" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A428" s="4"/>
       <c r="B428" s="4"/>
       <c r="C428" s="4"/>
@@ -18257,7 +18341,7 @@
       <c r="AI428" s="4"/>
       <c r="AJ428" s="4"/>
     </row>
-    <row r="429" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A429" s="4"/>
       <c r="B429" s="4"/>
       <c r="C429" s="4"/>
@@ -18295,7 +18379,7 @@
       <c r="AI429" s="4"/>
       <c r="AJ429" s="4"/>
     </row>
-    <row r="430" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A430" s="4"/>
       <c r="B430" s="4"/>
       <c r="C430" s="4"/>
@@ -18333,7 +18417,7 @@
       <c r="AI430" s="4"/>
       <c r="AJ430" s="4"/>
     </row>
-    <row r="431" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A431" s="4"/>
       <c r="B431" s="4"/>
       <c r="C431" s="4"/>
@@ -18371,7 +18455,7 @@
       <c r="AI431" s="4"/>
       <c r="AJ431" s="4"/>
     </row>
-    <row r="432" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A432" s="4"/>
       <c r="B432" s="4"/>
       <c r="C432" s="4"/>
@@ -18409,7 +18493,7 @@
       <c r="AI432" s="4"/>
       <c r="AJ432" s="4"/>
     </row>
-    <row r="433" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A433" s="4"/>
       <c r="B433" s="4"/>
       <c r="C433" s="4"/>
@@ -18447,7 +18531,7 @@
       <c r="AI433" s="4"/>
       <c r="AJ433" s="4"/>
     </row>
-    <row r="434" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A434" s="4"/>
       <c r="B434" s="4"/>
       <c r="C434" s="4"/>
@@ -18485,7 +18569,7 @@
       <c r="AI434" s="4"/>
       <c r="AJ434" s="4"/>
     </row>
-    <row r="435" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A435" s="4"/>
       <c r="B435" s="4"/>
       <c r="C435" s="4"/>
@@ -18523,7 +18607,7 @@
       <c r="AI435" s="4"/>
       <c r="AJ435" s="4"/>
     </row>
-    <row r="436" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A436" s="4"/>
       <c r="B436" s="4"/>
       <c r="C436" s="4"/>
@@ -18561,7 +18645,7 @@
       <c r="AI436" s="4"/>
       <c r="AJ436" s="4"/>
     </row>
-    <row r="437" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A437" s="4"/>
       <c r="B437" s="4"/>
       <c r="C437" s="4"/>
@@ -18599,7 +18683,7 @@
       <c r="AI437" s="4"/>
       <c r="AJ437" s="4"/>
     </row>
-    <row r="438" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A438" s="4"/>
       <c r="B438" s="4"/>
       <c r="C438" s="4"/>
@@ -18637,7 +18721,7 @@
       <c r="AI438" s="4"/>
       <c r="AJ438" s="4"/>
     </row>
-    <row r="439" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A439" s="4"/>
       <c r="B439" s="4"/>
       <c r="C439" s="4"/>
@@ -18675,7 +18759,7 @@
       <c r="AI439" s="4"/>
       <c r="AJ439" s="4"/>
     </row>
-    <row r="440" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A440" s="4"/>
       <c r="B440" s="4"/>
       <c r="C440" s="4"/>
@@ -18713,7 +18797,7 @@
       <c r="AI440" s="4"/>
       <c r="AJ440" s="4"/>
     </row>
-    <row r="441" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A441" s="4"/>
       <c r="B441" s="4"/>
       <c r="C441" s="4"/>
@@ -18751,7 +18835,7 @@
       <c r="AI441" s="4"/>
       <c r="AJ441" s="4"/>
     </row>
-    <row r="442" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A442" s="4"/>
       <c r="B442" s="4"/>
       <c r="C442" s="4"/>
@@ -18789,7 +18873,7 @@
       <c r="AI442" s="4"/>
       <c r="AJ442" s="4"/>
     </row>
-    <row r="443" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A443" s="4"/>
       <c r="B443" s="4"/>
       <c r="C443" s="4"/>
@@ -18827,7 +18911,7 @@
       <c r="AI443" s="4"/>
       <c r="AJ443" s="4"/>
     </row>
-    <row r="444" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A444" s="4"/>
       <c r="B444" s="4"/>
       <c r="C444" s="4"/>
@@ -18865,7 +18949,7 @@
       <c r="AI444" s="4"/>
       <c r="AJ444" s="4"/>
     </row>
-    <row r="445" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A445" s="4"/>
       <c r="B445" s="4"/>
       <c r="C445" s="4"/>
@@ -18903,7 +18987,7 @@
       <c r="AI445" s="4"/>
       <c r="AJ445" s="4"/>
     </row>
-    <row r="446" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A446" s="4"/>
       <c r="B446" s="4"/>
       <c r="C446" s="4"/>
@@ -18941,7 +19025,7 @@
       <c r="AI446" s="4"/>
       <c r="AJ446" s="4"/>
     </row>
-    <row r="447" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A447" s="4"/>
       <c r="B447" s="4"/>
       <c r="C447" s="4"/>
@@ -18979,7 +19063,7 @@
       <c r="AI447" s="4"/>
       <c r="AJ447" s="4"/>
     </row>
-    <row r="448" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A448" s="4"/>
       <c r="B448" s="4"/>
       <c r="C448" s="4"/>
@@ -19017,7 +19101,7 @@
       <c r="AI448" s="4"/>
       <c r="AJ448" s="4"/>
     </row>
-    <row r="449" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A449" s="4"/>
       <c r="B449" s="4"/>
       <c r="C449" s="4"/>
@@ -19055,7 +19139,7 @@
       <c r="AI449" s="4"/>
       <c r="AJ449" s="4"/>
     </row>
-    <row r="450" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A450" s="4"/>
       <c r="B450" s="4"/>
       <c r="C450" s="4"/>
@@ -19093,7 +19177,7 @@
       <c r="AI450" s="4"/>
       <c r="AJ450" s="4"/>
     </row>
-    <row r="451" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A451" s="4"/>
       <c r="B451" s="4"/>
       <c r="C451" s="4"/>
@@ -19131,7 +19215,7 @@
       <c r="AI451" s="4"/>
       <c r="AJ451" s="4"/>
     </row>
-    <row r="452" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A452" s="4"/>
       <c r="B452" s="4"/>
       <c r="C452" s="4"/>
@@ -19169,7 +19253,7 @@
       <c r="AI452" s="4"/>
       <c r="AJ452" s="4"/>
     </row>
-    <row r="453" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A453" s="4"/>
       <c r="B453" s="4"/>
       <c r="C453" s="4"/>
@@ -19207,7 +19291,7 @@
       <c r="AI453" s="4"/>
       <c r="AJ453" s="4"/>
     </row>
-    <row r="454" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A454" s="4"/>
       <c r="B454" s="4"/>
       <c r="C454" s="4"/>
@@ -19245,7 +19329,7 @@
       <c r="AI454" s="4"/>
       <c r="AJ454" s="4"/>
     </row>
-    <row r="455" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A455" s="4"/>
       <c r="B455" s="4"/>
       <c r="C455" s="4"/>
@@ -19283,7 +19367,7 @@
       <c r="AI455" s="4"/>
       <c r="AJ455" s="4"/>
     </row>
-    <row r="456" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A456" s="4"/>
       <c r="B456" s="4"/>
       <c r="C456" s="4"/>
@@ -19321,7 +19405,7 @@
       <c r="AI456" s="4"/>
       <c r="AJ456" s="4"/>
     </row>
-    <row r="457" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A457" s="4"/>
       <c r="B457" s="4"/>
       <c r="C457" s="4"/>
@@ -19359,7 +19443,7 @@
       <c r="AI457" s="4"/>
       <c r="AJ457" s="4"/>
     </row>
-    <row r="458" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A458" s="4"/>
       <c r="B458" s="4"/>
       <c r="C458" s="4"/>
@@ -19397,7 +19481,7 @@
       <c r="AI458" s="4"/>
       <c r="AJ458" s="4"/>
     </row>
-    <row r="459" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A459" s="4"/>
       <c r="B459" s="4"/>
       <c r="C459" s="4"/>
@@ -19435,7 +19519,7 @@
       <c r="AI459" s="4"/>
       <c r="AJ459" s="4"/>
     </row>
-    <row r="460" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A460" s="4"/>
       <c r="B460" s="4"/>
       <c r="C460" s="4"/>
@@ -19473,7 +19557,7 @@
       <c r="AI460" s="4"/>
       <c r="AJ460" s="4"/>
     </row>
-    <row r="461" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A461" s="4"/>
       <c r="B461" s="4"/>
       <c r="C461" s="4"/>
@@ -19511,7 +19595,7 @@
       <c r="AI461" s="4"/>
       <c r="AJ461" s="4"/>
     </row>
-    <row r="462" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A462" s="4"/>
       <c r="B462" s="4"/>
       <c r="C462" s="4"/>
@@ -19549,7 +19633,7 @@
       <c r="AI462" s="4"/>
       <c r="AJ462" s="4"/>
     </row>
-    <row r="463" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A463" s="4"/>
       <c r="B463" s="4"/>
       <c r="C463" s="4"/>
@@ -19587,7 +19671,7 @@
       <c r="AI463" s="4"/>
       <c r="AJ463" s="4"/>
     </row>
-    <row r="464" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A464" s="4"/>
       <c r="B464" s="4"/>
       <c r="C464" s="4"/>
@@ -19625,7 +19709,7 @@
       <c r="AI464" s="4"/>
       <c r="AJ464" s="4"/>
     </row>
-    <row r="465" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A465" s="4"/>
       <c r="B465" s="4"/>
       <c r="C465" s="4"/>
@@ -19663,7 +19747,7 @@
       <c r="AI465" s="4"/>
       <c r="AJ465" s="4"/>
     </row>
-    <row r="466" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A466" s="4"/>
       <c r="B466" s="4"/>
       <c r="C466" s="4"/>
@@ -19701,7 +19785,7 @@
       <c r="AI466" s="4"/>
       <c r="AJ466" s="4"/>
     </row>
-    <row r="467" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A467" s="4"/>
       <c r="B467" s="4"/>
       <c r="C467" s="4"/>
@@ -19739,7 +19823,7 @@
       <c r="AI467" s="4"/>
       <c r="AJ467" s="4"/>
     </row>
-    <row r="468" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A468" s="4"/>
       <c r="B468" s="4"/>
       <c r="C468" s="4"/>
@@ -19777,7 +19861,7 @@
       <c r="AI468" s="4"/>
       <c r="AJ468" s="4"/>
     </row>
-    <row r="469" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A469" s="4"/>
       <c r="B469" s="4"/>
       <c r="C469" s="4"/>
@@ -19815,7 +19899,7 @@
       <c r="AI469" s="4"/>
       <c r="AJ469" s="4"/>
     </row>
-    <row r="470" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A470" s="4"/>
       <c r="B470" s="4"/>
       <c r="C470" s="4"/>
@@ -19853,7 +19937,7 @@
       <c r="AI470" s="4"/>
       <c r="AJ470" s="4"/>
     </row>
-    <row r="471" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A471" s="4"/>
       <c r="B471" s="4"/>
       <c r="C471" s="4"/>
@@ -19891,7 +19975,7 @@
       <c r="AI471" s="4"/>
       <c r="AJ471" s="4"/>
     </row>
-    <row r="472" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A472" s="4"/>
       <c r="B472" s="4"/>
       <c r="C472" s="4"/>
@@ -19929,7 +20013,7 @@
       <c r="AI472" s="4"/>
       <c r="AJ472" s="4"/>
     </row>
-    <row r="473" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A473" s="4"/>
       <c r="B473" s="4"/>
       <c r="C473" s="4"/>
@@ -19967,7 +20051,7 @@
       <c r="AI473" s="4"/>
       <c r="AJ473" s="4"/>
     </row>
-    <row r="474" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A474" s="4"/>
       <c r="B474" s="4"/>
       <c r="C474" s="4"/>
@@ -20005,7 +20089,7 @@
       <c r="AI474" s="4"/>
       <c r="AJ474" s="4"/>
     </row>
-    <row r="475" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A475" s="4"/>
       <c r="B475" s="4"/>
       <c r="C475" s="4"/>
@@ -20043,7 +20127,7 @@
       <c r="AI475" s="4"/>
       <c r="AJ475" s="4"/>
     </row>
-    <row r="476" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A476" s="4"/>
       <c r="B476" s="4"/>
       <c r="C476" s="4"/>
@@ -20081,7 +20165,7 @@
       <c r="AI476" s="4"/>
       <c r="AJ476" s="4"/>
     </row>
-    <row r="477" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A477" s="4"/>
       <c r="B477" s="4"/>
       <c r="C477" s="4"/>
@@ -20119,7 +20203,7 @@
       <c r="AI477" s="4"/>
       <c r="AJ477" s="4"/>
     </row>
-    <row r="478" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A478" s="4"/>
       <c r="B478" s="4"/>
       <c r="C478" s="4"/>
@@ -20157,7 +20241,7 @@
       <c r="AI478" s="4"/>
       <c r="AJ478" s="4"/>
     </row>
-    <row r="479" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A479" s="4"/>
       <c r="B479" s="4"/>
       <c r="C479" s="4"/>
@@ -20195,7 +20279,7 @@
       <c r="AI479" s="4"/>
       <c r="AJ479" s="4"/>
     </row>
-    <row r="480" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A480" s="4"/>
       <c r="B480" s="4"/>
       <c r="C480" s="4"/>
@@ -20233,7 +20317,7 @@
       <c r="AI480" s="4"/>
       <c r="AJ480" s="4"/>
     </row>
-    <row r="481" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A481" s="4"/>
       <c r="B481" s="4"/>
       <c r="C481" s="4"/>
@@ -20271,7 +20355,7 @@
       <c r="AI481" s="4"/>
       <c r="AJ481" s="4"/>
     </row>
-    <row r="482" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A482" s="4"/>
       <c r="B482" s="4"/>
       <c r="C482" s="4"/>
@@ -20309,7 +20393,7 @@
       <c r="AI482" s="4"/>
       <c r="AJ482" s="4"/>
     </row>
-    <row r="483" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A483" s="4"/>
       <c r="B483" s="4"/>
       <c r="C483" s="4"/>
@@ -20347,7 +20431,7 @@
       <c r="AI483" s="4"/>
       <c r="AJ483" s="4"/>
     </row>
-    <row r="484" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A484" s="4"/>
       <c r="B484" s="4"/>
       <c r="C484" s="4"/>
@@ -20385,7 +20469,7 @@
       <c r="AI484" s="4"/>
       <c r="AJ484" s="4"/>
     </row>
-    <row r="485" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A485" s="4"/>
       <c r="B485" s="4"/>
       <c r="C485" s="4"/>
@@ -20423,7 +20507,7 @@
       <c r="AI485" s="4"/>
       <c r="AJ485" s="4"/>
     </row>
-    <row r="486" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A486" s="4"/>
       <c r="B486" s="4"/>
       <c r="C486" s="4"/>
@@ -20461,7 +20545,7 @@
       <c r="AI486" s="4"/>
       <c r="AJ486" s="4"/>
     </row>
-    <row r="487" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A487" s="4"/>
       <c r="B487" s="4"/>
       <c r="C487" s="4"/>
@@ -20499,7 +20583,7 @@
       <c r="AI487" s="4"/>
       <c r="AJ487" s="4"/>
     </row>
-    <row r="488" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A488" s="4"/>
       <c r="B488" s="4"/>
       <c r="C488" s="4"/>
@@ -20537,7 +20621,7 @@
       <c r="AI488" s="4"/>
       <c r="AJ488" s="4"/>
     </row>
-    <row r="489" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A489" s="4"/>
       <c r="B489" s="4"/>
       <c r="C489" s="4"/>
@@ -20575,7 +20659,7 @@
       <c r="AI489" s="4"/>
       <c r="AJ489" s="4"/>
     </row>
-    <row r="490" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A490" s="4"/>
       <c r="B490" s="4"/>
       <c r="C490" s="4"/>
@@ -20613,7 +20697,7 @@
       <c r="AI490" s="4"/>
       <c r="AJ490" s="4"/>
     </row>
-    <row r="491" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A491" s="4"/>
       <c r="B491" s="4"/>
       <c r="C491" s="4"/>
@@ -20651,7 +20735,7 @@
       <c r="AI491" s="4"/>
       <c r="AJ491" s="4"/>
     </row>
-    <row r="492" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A492" s="4"/>
       <c r="B492" s="4"/>
       <c r="C492" s="4"/>
@@ -20689,7 +20773,7 @@
       <c r="AI492" s="4"/>
       <c r="AJ492" s="4"/>
     </row>
-    <row r="493" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A493" s="4"/>
       <c r="B493" s="4"/>
       <c r="C493" s="4"/>
@@ -20727,7 +20811,7 @@
       <c r="AI493" s="4"/>
       <c r="AJ493" s="4"/>
     </row>
-    <row r="494" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A494" s="4"/>
       <c r="B494" s="4"/>
       <c r="C494" s="4"/>
@@ -20765,7 +20849,7 @@
       <c r="AI494" s="4"/>
       <c r="AJ494" s="4"/>
     </row>
-    <row r="495" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A495" s="4"/>
       <c r="B495" s="4"/>
       <c r="C495" s="4"/>
@@ -20803,7 +20887,7 @@
       <c r="AI495" s="4"/>
       <c r="AJ495" s="4"/>
     </row>
-    <row r="496" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A496" s="4"/>
       <c r="B496" s="4"/>
       <c r="C496" s="4"/>
@@ -20841,7 +20925,7 @@
       <c r="AI496" s="4"/>
       <c r="AJ496" s="4"/>
     </row>
-    <row r="497" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A497" s="4"/>
       <c r="B497" s="4"/>
       <c r="C497" s="4"/>
@@ -20879,7 +20963,7 @@
       <c r="AI497" s="4"/>
       <c r="AJ497" s="4"/>
     </row>
-    <row r="498" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A498" s="4"/>
       <c r="B498" s="4"/>
       <c r="C498" s="4"/>
@@ -20917,7 +21001,7 @@
       <c r="AI498" s="4"/>
       <c r="AJ498" s="4"/>
     </row>
-    <row r="499" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A499" s="4"/>
       <c r="B499" s="4"/>
       <c r="C499" s="4"/>
@@ -20955,7 +21039,7 @@
       <c r="AI499" s="4"/>
       <c r="AJ499" s="4"/>
     </row>
-    <row r="500" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A500" s="4"/>
       <c r="B500" s="4"/>
       <c r="C500" s="4"/>
@@ -20993,7 +21077,7 @@
       <c r="AI500" s="4"/>
       <c r="AJ500" s="4"/>
     </row>
-    <row r="501" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A501" s="4"/>
       <c r="B501" s="4"/>
       <c r="C501" s="4"/>
@@ -21031,7 +21115,7 @@
       <c r="AI501" s="4"/>
       <c r="AJ501" s="4"/>
     </row>
-    <row r="502" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A502" s="4"/>
       <c r="B502" s="4"/>
       <c r="C502" s="4"/>
@@ -21069,7 +21153,7 @@
       <c r="AI502" s="4"/>
       <c r="AJ502" s="4"/>
     </row>
-    <row r="503" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A503" s="4"/>
       <c r="B503" s="4"/>
       <c r="C503" s="4"/>
@@ -21107,7 +21191,7 @@
       <c r="AI503" s="4"/>
       <c r="AJ503" s="4"/>
     </row>
-    <row r="504" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A504" s="4"/>
       <c r="B504" s="4"/>
       <c r="C504" s="4"/>
@@ -21145,7 +21229,7 @@
       <c r="AI504" s="4"/>
       <c r="AJ504" s="4"/>
     </row>
-    <row r="505" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A505" s="4"/>
       <c r="B505" s="4"/>
       <c r="C505" s="4"/>
@@ -21183,7 +21267,7 @@
       <c r="AI505" s="4"/>
       <c r="AJ505" s="4"/>
     </row>
-    <row r="506" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A506" s="4"/>
       <c r="B506" s="4"/>
       <c r="C506" s="4"/>
@@ -21221,7 +21305,7 @@
       <c r="AI506" s="4"/>
       <c r="AJ506" s="4"/>
     </row>
-    <row r="507" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A507" s="4"/>
       <c r="B507" s="4"/>
       <c r="C507" s="4"/>
@@ -21259,7 +21343,7 @@
       <c r="AI507" s="4"/>
       <c r="AJ507" s="4"/>
     </row>
-    <row r="508" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A508" s="4"/>
       <c r="B508" s="4"/>
       <c r="C508" s="4"/>
@@ -21297,7 +21381,7 @@
       <c r="AI508" s="4"/>
       <c r="AJ508" s="4"/>
     </row>
-    <row r="509" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A509" s="4"/>
       <c r="B509" s="4"/>
       <c r="C509" s="4"/>
@@ -21335,7 +21419,7 @@
       <c r="AI509" s="4"/>
       <c r="AJ509" s="4"/>
     </row>
-    <row r="510" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A510" s="4"/>
       <c r="B510" s="4"/>
       <c r="C510" s="4"/>
@@ -21373,7 +21457,7 @@
       <c r="AI510" s="4"/>
       <c r="AJ510" s="4"/>
     </row>
-    <row r="511" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A511" s="4"/>
       <c r="B511" s="4"/>
       <c r="C511" s="4"/>
@@ -21411,7 +21495,7 @@
       <c r="AI511" s="4"/>
       <c r="AJ511" s="4"/>
     </row>
-    <row r="512" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A512" s="4"/>
       <c r="B512" s="4"/>
       <c r="C512" s="4"/>
@@ -21449,7 +21533,7 @@
       <c r="AI512" s="4"/>
       <c r="AJ512" s="4"/>
     </row>
-    <row r="513" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A513" s="4"/>
       <c r="B513" s="4"/>
       <c r="C513" s="4"/>
@@ -21487,7 +21571,7 @@
       <c r="AI513" s="4"/>
       <c r="AJ513" s="4"/>
     </row>
-    <row r="514" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A514" s="4"/>
       <c r="B514" s="4"/>
       <c r="C514" s="4"/>
@@ -21525,7 +21609,7 @@
       <c r="AI514" s="4"/>
       <c r="AJ514" s="4"/>
     </row>
-    <row r="515" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A515" s="4"/>
       <c r="B515" s="4"/>
       <c r="C515" s="4"/>
@@ -21563,7 +21647,7 @@
       <c r="AI515" s="4"/>
       <c r="AJ515" s="4"/>
     </row>
-    <row r="516" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A516" s="4"/>
       <c r="B516" s="4"/>
       <c r="C516" s="4"/>
@@ -21601,7 +21685,7 @@
       <c r="AI516" s="4"/>
       <c r="AJ516" s="4"/>
     </row>
-    <row r="517" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A517" s="4"/>
       <c r="B517" s="4"/>
       <c r="C517" s="4"/>
@@ -21639,7 +21723,7 @@
       <c r="AI517" s="4"/>
       <c r="AJ517" s="4"/>
     </row>
-    <row r="518" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A518" s="4"/>
       <c r="B518" s="4"/>
       <c r="C518" s="4"/>
@@ -21677,7 +21761,7 @@
       <c r="AI518" s="4"/>
       <c r="AJ518" s="4"/>
     </row>
-    <row r="519" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A519" s="4"/>
       <c r="B519" s="4"/>
       <c r="C519" s="4"/>
@@ -21715,7 +21799,7 @@
       <c r="AI519" s="4"/>
       <c r="AJ519" s="4"/>
     </row>
-    <row r="520" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A520" s="4"/>
       <c r="B520" s="4"/>
       <c r="C520" s="4"/>
@@ -21753,7 +21837,7 @@
       <c r="AI520" s="4"/>
       <c r="AJ520" s="4"/>
     </row>
-    <row r="521" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A521" s="4"/>
       <c r="B521" s="4"/>
       <c r="C521" s="4"/>
@@ -21791,7 +21875,7 @@
       <c r="AI521" s="4"/>
       <c r="AJ521" s="4"/>
     </row>
-    <row r="522" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A522" s="4"/>
       <c r="B522" s="4"/>
       <c r="C522" s="4"/>
@@ -21829,7 +21913,7 @@
       <c r="AI522" s="4"/>
       <c r="AJ522" s="4"/>
     </row>
-    <row r="523" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A523" s="4"/>
       <c r="B523" s="4"/>
       <c r="C523" s="4"/>
@@ -21867,7 +21951,7 @@
       <c r="AI523" s="4"/>
       <c r="AJ523" s="4"/>
     </row>
-    <row r="524" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A524" s="4"/>
       <c r="B524" s="4"/>
       <c r="C524" s="4"/>
@@ -21905,7 +21989,7 @@
       <c r="AI524" s="4"/>
       <c r="AJ524" s="4"/>
     </row>
-    <row r="525" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A525" s="4"/>
       <c r="B525" s="4"/>
       <c r="C525" s="4"/>
@@ -21943,7 +22027,7 @@
       <c r="AI525" s="4"/>
       <c r="AJ525" s="4"/>
     </row>
-    <row r="526" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A526" s="4"/>
       <c r="B526" s="4"/>
       <c r="C526" s="4"/>
@@ -21981,7 +22065,7 @@
       <c r="AI526" s="4"/>
       <c r="AJ526" s="4"/>
     </row>
-    <row r="527" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A527" s="4"/>
       <c r="B527" s="4"/>
       <c r="C527" s="4"/>
@@ -22019,7 +22103,7 @@
       <c r="AI527" s="4"/>
       <c r="AJ527" s="4"/>
     </row>
-    <row r="528" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A528" s="4"/>
       <c r="B528" s="4"/>
       <c r="C528" s="4"/>
@@ -22057,7 +22141,7 @@
       <c r="AI528" s="4"/>
       <c r="AJ528" s="4"/>
     </row>
-    <row r="529" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A529" s="4"/>
       <c r="B529" s="4"/>
       <c r="C529" s="4"/>
@@ -22095,7 +22179,7 @@
       <c r="AI529" s="4"/>
       <c r="AJ529" s="4"/>
     </row>
-    <row r="530" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A530" s="4"/>
       <c r="B530" s="4"/>
       <c r="C530" s="4"/>
@@ -22133,7 +22217,7 @@
       <c r="AI530" s="4"/>
       <c r="AJ530" s="4"/>
     </row>
-    <row r="531" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A531" s="4"/>
       <c r="B531" s="4"/>
       <c r="C531" s="4"/>
@@ -22171,7 +22255,7 @@
       <c r="AI531" s="4"/>
       <c r="AJ531" s="4"/>
     </row>
-    <row r="532" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A532" s="4"/>
       <c r="B532" s="4"/>
       <c r="C532" s="4"/>
@@ -22209,7 +22293,7 @@
       <c r="AI532" s="4"/>
       <c r="AJ532" s="4"/>
     </row>
-    <row r="533" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A533" s="4"/>
       <c r="B533" s="4"/>
       <c r="C533" s="4"/>
@@ -22247,7 +22331,7 @@
       <c r="AI533" s="4"/>
       <c r="AJ533" s="4"/>
     </row>
-    <row r="534" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:36" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A534" s="4"/>
       <c r="B534" s="4"/>
       <c r="C534" s="4"/>
@@ -22303,12 +22387,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.3984375" customWidth="1"/>
+    <col min="1" max="1" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -22403,9 +22487,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B2" s="41">
         <v>0.5</v>
@@ -22414,79 +22498,79 @@
         <v>0</v>
       </c>
       <c r="D2" s="42">
-        <f>'Inflation Reduction Act'!B88</f>
+        <f>'IRA_Modifying by Korea data'!B88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="E2" s="42">
-        <f>'Inflation Reduction Act'!C88</f>
+        <f>'IRA_Modifying by Korea data'!C88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="F2" s="42">
-        <f>'Inflation Reduction Act'!D88</f>
+        <f>'IRA_Modifying by Korea data'!D88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="G2" s="42">
-        <f>'Inflation Reduction Act'!E88</f>
+        <f>'IRA_Modifying by Korea data'!E88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="H2" s="42">
-        <f>'Inflation Reduction Act'!F88</f>
+        <f>'IRA_Modifying by Korea data'!F88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="I2" s="42">
-        <f>'Inflation Reduction Act'!G88</f>
+        <f>'IRA_Modifying by Korea data'!G88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="J2" s="42">
-        <f>'Inflation Reduction Act'!H88</f>
+        <f>'IRA_Modifying by Korea data'!H88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="K2" s="42">
-        <f>'Inflation Reduction Act'!I88</f>
+        <f>'IRA_Modifying by Korea data'!I88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="L2" s="42">
-        <f>'Inflation Reduction Act'!J88</f>
+        <f>'IRA_Modifying by Korea data'!J88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="M2" s="42">
-        <f>'Inflation Reduction Act'!K88</f>
+        <f>'IRA_Modifying by Korea data'!K88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="N2" s="42">
-        <f>'Inflation Reduction Act'!L88</f>
+        <f>'IRA_Modifying by Korea data'!L88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="O2" s="42">
-        <f>'Inflation Reduction Act'!M88</f>
+        <f>'IRA_Modifying by Korea data'!M88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="P2" s="42">
-        <f>'Inflation Reduction Act'!N88</f>
+        <f>'IRA_Modifying by Korea data'!N88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="Q2" s="42">
-        <f>'Inflation Reduction Act'!O88</f>
+        <f>'IRA_Modifying by Korea data'!O88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="R2" s="42">
-        <f>'Inflation Reduction Act'!P88</f>
+        <f>'IRA_Modifying by Korea data'!P88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="S2" s="42">
-        <f>'Inflation Reduction Act'!Q88</f>
+        <f>'IRA_Modifying by Korea data'!Q88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="T2" s="42">
-        <f>'Inflation Reduction Act'!R88</f>
+        <f>'IRA_Modifying by Korea data'!R88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="U2" s="42">
-        <f>'Inflation Reduction Act'!S88</f>
+        <f>'IRA_Modifying by Korea data'!S88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="V2" s="42">
-        <f>'Inflation Reduction Act'!T88</f>
+        <f>'IRA_Modifying by Korea data'!T88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="W2" s="42">
@@ -22525,6 +22609,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -22668,29 +22767,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DAAFF62-1415-465A-802F-0CE5E395A9C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D40D37B6-66ED-4061-AEAD-FDD3843AB104}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E457163-2DA1-4E36-A472-23C00CA8EB0A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E457163-2DA1-4E36-A472-23C00CA8EB0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D40D37B6-66ED-4061-AEAD-FDD3843AB104}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DAAFF62-1415-465A-802F-0CE5E395A9C8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>